--- a/data/reference/ucr_courses.xlsx
+++ b/data/reference/ucr_courses.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S152"/>
+  <dimension ref="A1:O151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -377,77 +377,57 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>description2</t>
+          <t>preq1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>preq1</t>
+          <t>deplabel</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>deplabel</t>
+          <t>tracklabel</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>tracklabel</t>
+          <t>2025h2</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>CRG</t>
+          <t>2026h1</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025h2</t>
+          <t>2026h2</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2026h1</t>
+          <t>2027h1</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2026h2</t>
+          <t>2027h2</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2027h1</t>
+          <t>2028h1</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>2027h2</t>
+          <t>2028h2</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>2028h1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>2028h2</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
           <t>2029h1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>2029h2</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>2030h1</t>
         </is>
       </c>
     </row>
@@ -474,27 +454,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>This course is a first-year requirement and aims to stimulate personal development, namely, being able to actively, consciously and ethically orientate oneself in relation to others and the world. It supports the development of core personal and academic skills that enhance critical thinking and independent learning. It seeks to improve and develop academic writing and presenting skills and helps students develop the foundational skills and attitudes to reflect on societal issues and engage with societal partners.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Academic Core</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Academic Core</t>
+          <t>Personal &amp; Professional Development</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Personal &amp; Professional Development</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -502,6 +477,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>X</t>
@@ -518,26 +498,6 @@
         </is>
       </c>
       <c r="O2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -566,27 +526,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>This course describes the most widely accepted accounting theory and practice with an emphasis on using and analyzing the information in financial statements. Students learn how to comprehend a typical corporate annual report and to use accounting as a tool in understanding how economic events affect business.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -595,16 +550,6 @@
         </is>
       </c>
       <c r="N3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -633,40 +578,30 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>This course examines how organizations are structured and evolve over time. It explores how organizational design relates to strategy, external environment, human behavior, culture, governance and performance. A particular emphasis is put on discussing the concept and enabling capabilities of organizational agility required to navigate a fast-paced world and tackle increased uncertainty.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
           <t>Business</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -695,40 +630,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Businesses and entrepreneurs are confronted with legal complexity not only at the domestic level but particularly across divergent legal systems. This course presents a survey of the most essential fields of business law: contracts law, company law, trade law, intellectual property, and dispute resolution. An ultimate aim of the course is to critically examine the impact of globalization and digitization on the development of business law.</t>
+          <t>BENGATE101</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BENGATE101</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
           <t>Business</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -757,27 +677,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>This course develops practical financial decision-making skills through case studies and real-world applications. Students learn to analyze financial data, assess risks, and make informed investment, budgeting, and business decisions that enhance value, financial security, and long-term planning.</t>
+          <t>BENGATE101</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BENGATE101</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -785,7 +700,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -814,50 +729,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Explore how individuals, firms, and societies make economic decisions. This course introduces key concepts from both microeconomics and macroeconomics, including markets, incentives, and the principles of supply and demand, and provides a foundation for analyzing real-world economic issues.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -886,27 +776,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Study the economy as a whole through topics such as national income, economic growth, inflation, and unemployment. Understand how governments and central banks use fiscal and monetary policies to influence economic performance over time. The course also explores business cycles, international trade, and economic crises, preparing students to evaluate policy debates and global economic trends.</t>
+          <t>BENGATE102</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BENGATE102</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -920,16 +805,6 @@
         </is>
       </c>
       <c r="N8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -958,27 +833,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Study how consumers and producers make decisions under scarcity. Explore key concepts such as rational choice, decision-making under uncertainty, and non-egoistic preferences. Analyze market structures, strategic interactions, and factor markets. Learn how markets function and examine the impact of regulation. Develop analytical tools to better understand behavior and engage with empirical research.</t>
+          <t>BENGATE102</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BENGATE102</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
           <t>Economics</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -992,16 +862,6 @@
         </is>
       </c>
       <c r="O9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1030,40 +890,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Investigate the role of government in the economy, focusing on how public policy influences efficiency and equity. The course covers taxation, public goods, externalities, and government spending. Combining theoretical models with empirical evidence, it evaluates how different policies affect societal welfare.</t>
+          <t>BENGATE102</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BENGATE102</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
           <t>Economics</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1092,35 +937,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Econometrics supplies tools to analyze data to answer questions of causality and prediction. In this course you learn three estimators—Ordinary Least Squares, Generalized Least Squares, and Instrumental Variables—and three tests—t-test, F-test, and LM-test. Understanding the basic rules of econometrics, particularly the sampling distribution concept, is key, and the course uses Monte Carlo simulations in Stata to visualize it. Tools are applied to estimate economic relationships and make predictions, and students write an empirical paper.</t>
+          <t>BENGATE102</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BENGATE102</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1149,35 +984,30 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>This course integrates insights from psychology into economic theory to better understand how people make decisions. Learn how actual behavior deviates from the predictions of traditional economic models due to biases, heuristics, and framing. Through experiments, students will deepen their understanding of decision-making and its implications for economic theory and practice.</t>
+          <t>BENGATE102</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BENGATE102</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1206,50 +1036,30 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>You will learn how to function in a ‘real-world’ design and development team for consumer products. We go through the phases of design and development: probe customer needs, translate these into a product concept, develop a fabrication method, analyze sustainability, analyze costs and proceeds. Design and development involves interviewing customers, brainstorming, laboratory experiments, quantitative modeling, constructing a prototype, and considering protection of intellectual property.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
           <t>Entrepreneurship</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1278,27 +1088,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>This course unpacks what drives consumer engagement with brands and how marketers build customer trust responsibly. It introduces key marketing concepts, consumer psychology, AI/technology-driven marketing innovation, and brand and communication strategies. Students will explore real-life case studies, develop a strategic marketing plan and learn how marketers build sustainable brand strategies.</t>
+          <t>BENGATE102</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BENGATE102</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
           <t>Entrepreneurship</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1312,16 +1117,6 @@
         </is>
       </c>
       <c r="O14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1350,27 +1145,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The course explores how companies develop strategies and drive responsible digital transformation amid rapid technology change impacting the economy and society. Students develop a strategic plan, from vision to execution, and identify digital value opportunities. Using industry cases, they gain foresight into digital technologies and their impact on strategy, business models and social responsibilities.</t>
+          <t>BENGATE101</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BENGATE101</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
           <t>Entrepreneurship</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1379,16 +1169,6 @@
         </is>
       </c>
       <c r="O15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1417,27 +1197,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>See how companies figure out what customers love and what they don’t. You’ll plan and carry out real research, analyze what you find, and share your results. Our course shows you how to gather opinions and turn them into smart business ideas—perfect for future marketers, analysts, or entrepreneurs.</t>
+          <t>BENGATE101</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BENGATE101</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
           <t>Entrepreneurship</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1445,7 +1220,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1474,27 +1249,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>This course examines the institutional, political and cultural forces shaping global businesses. It first explores how international companies operate, then centers on key global challenges including cross-border governance, corporate responsibility, geopolitical strategies and global trade. It provides a comprehensive understanding of today’s complex international business environment.</t>
+          <t>BENGATE101</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BENGATE101</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
           <t>Entrepreneurship</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1502,7 +1272,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1531,27 +1301,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Through experiential learning, students turn their own bold ideas into new ventures. No prior business expertise is required as teams work on a startup project from ideation to final pitch while gaining business and entrepreneurial skills in areas such as design thinking, business model and customer validation. The class fosters creativity and collaboration to drive business and social innovation.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Gateway</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>G</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1565,16 +1330,6 @@
         </is>
       </c>
       <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1603,27 +1358,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Research Methods &amp; Statistics gives you a strong foundation in how business management—and social and behavioral sciences—move from mere practices to true fields of scientific study. You’ll learn how to plan research logically, from designing studies to working with real data using experimental and survey techniques. You’ll also study descriptive and inferential statistics, with a brief intro to multivariate tools.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
           <t>Gateway</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1637,16 +1387,6 @@
         </is>
       </c>
       <c r="O19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1675,27 +1415,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Personal Leadership provides a comprehensive introduction to leadership theory and practice, designed to help students discover their unique leadership style through self-awareness and practical skill-building. Through interactive workshops, reflective exercises, and real-world applications, students engage deeply with core leadership principles and develop the tools needed to lead confidently in any setting.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Leadership</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1709,16 +1444,6 @@
         </is>
       </c>
       <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1747,27 +1472,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>This course blends theory with practice from both fiction and the real world, helping you develop essential leadership skills. Learn how to inspire teams, sharpen your communication, take ethical decisions, and lead with confidence.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
           <t>Leadership</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1781,16 +1501,6 @@
         </is>
       </c>
       <c r="O21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1819,27 +1529,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Leadership &amp; Diversity Management explores how diverse perspectives and experiences shape effective leadership in dynamic, varied environments. Blending cutting-edge theories with hands-on practice, students develop the skills to lead with empathy, inclusivity, and adaptability. Through engaging case studies, interactive workshops, and reflective assessments, participants build awareness of diversity and learn to inspire ethical, collaborative teams.</t>
+          <t>BENGATE102</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BENGATE102</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
           <t>Leadership</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1847,7 +1552,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1876,27 +1581,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>This course offers Liberal Arts and Sciences students a deep dive into the psychological, social, and structural dynamics that shape workplaces. Through interactive case discussions, simulations, and real-world insights, students develop critical skills in motivation, leadership, group dynamics, and culture. By synthesizing research and applying theory to practice, participants gain the tools to navigate and influence diverse organizational environments effectively.</t>
+          <t>BENGATE102</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BENGATE102</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Leadership</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1910,16 +1610,6 @@
         </is>
       </c>
       <c r="N23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1948,40 +1638,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>How do you get to yes? In this course you will learn how to craft persuasive arguments, deploy the right language, negotiate more effectively, and influence decisions with confidence—whether in business, leadership, or life.</t>
+          <t>BENGATE102</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BENGATE102</t>
+          <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
           <t>Leadership</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2010,27 +1685,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Explores philosophical foundations and implications of AI. Examines the history of AI, ethical issues like interpretability, bias and alignment, debates about AI consciousness and implications for human nature.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2044,16 +1714,6 @@
         </is>
       </c>
       <c r="O25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2082,45 +1742,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Introduces planning techniques for AI systems in deterministic and non‑deterministic environments. Addresses uncertainty, partial observability, resource planning and optimizing behaviour under constraints.</t>
+          <t>DISGATE101</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>DISGATE101</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2149,27 +1789,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Focuses on mathematics of decision‑making, covering topics in discrete mathematics such as logic, patterns and structures, with applications to computer science and algorithm construction.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2178,16 +1813,6 @@
         </is>
       </c>
       <c r="N27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2216,27 +1841,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Covers computational methods for search problems in complex and adversarial environments. Includes uninformed and informed search, local and global search, adversarial games and constraint satisfaction problems.</t>
+          <t>DISGATE101</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DISGATE101</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2244,22 +1864,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="O28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2288,35 +1893,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Explores reinforcement learning. Covers theoretical frameworks and algorithms and requires students to implement algorithms and build agents using neural networks that learn through trial and error.</t>
+          <t>DISGATE101</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DISGATE101</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2345,40 +1940,30 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Introduces computer networks and operating systems. Covers how the internet works and the role of an OS in resource management and application support.</t>
+          <t>DISGATE101</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DISGATE101</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2407,27 +1992,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Introduces relational database management systems and SQL. Covers relational database theory, authorization, normalization and query processing.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2436,16 +2016,6 @@
         </is>
       </c>
       <c r="O31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2474,40 +2044,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Covers software design, creation, testing and maintenance. Uses C++ and Haskell and covers planning, requirements gathering, testing, deployment and maintenance through discussions and code reviews.</t>
+          <t>DISGATE101</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>DISGATE101</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
           <t>Computer Science</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2536,27 +2091,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Teaches design and analysis of algorithms and data structures, emphasizing performance analysis and focusing on prominent algorithms and data structures.</t>
+          <t>DISGATE101</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DISGATE101</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2570,16 +2120,6 @@
         </is>
       </c>
       <c r="N33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2608,40 +2148,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Studies modern algebraic algorithms and optimization methods. Emphasises algorithmic thinking and mathematical modelling of computational problems.</t>
+          <t>DISGATE101</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DISGATE101</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
           <t>Computer Science</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2670,27 +2195,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Develops foundational skills in data visualization, cleaning and manipulation. Explores spatial and text data and includes hands‑on work with datasets from various disciplines.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2719,26 +2244,6 @@
         </is>
       </c>
       <c r="O35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2767,27 +2272,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Covers core machine learning techniques from linear regression to advanced tree‑based methods. Discusses strengths and weaknesses and applies methods to real data from fields like medicine, physics and economics.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2801,16 +2301,6 @@
         </is>
       </c>
       <c r="N36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2839,50 +2329,30 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Covers processing and analysis of image data, including feature detection and tracking. Discusses applications in medicine, self‑driving vehicles, gaming, robotics and traffic management.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2911,27 +2381,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Explores theory and practice of neural networks. Students build basic networks and progress to complex networks for computer vision, and discuss recent developments in large language and image generation models.</t>
+          <t>DISGATE102</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>DISGATE102</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
           <t>Data Science</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2939,22 +2404,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="O38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2983,40 +2433,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Covers computational problems in robotics. Includes forward and inverse kinematics, motion planning, collision avoidance and robotic grasping and manipulation.</t>
+          <t>DISGATE102</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DISGATE102</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
           <t>Data Science</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3045,27 +2480,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Introduces programming and computer science. Covers structured programming, data constructs, testing, debugging and object‑oriented programming with Python, and develops computational problem‑solving skills.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Gateway</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>G</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3079,16 +2509,6 @@
         </is>
       </c>
       <c r="N40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3117,30 +2537,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Introduces linear algebra (vectors, matrices, eigenvalues) and calculus (limits, differentiation, integration) to construct and solve equations. Provides problem‑solving skills applicable across disciplines.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Gateway</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3151,16 +2566,6 @@
         </is>
       </c>
       <c r="O41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3189,27 +2594,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Introduces systems of equations, vectors, matrices and linear spaces with emphasis on visual and conceptual understanding. Applies concepts across fields and includes hands‑on exercises using computer algebra software.</t>
+          <t>DISGATE102</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DISGATE102</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3223,16 +2623,6 @@
         </is>
       </c>
       <c r="N42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3261,40 +2651,30 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Introduces numerical methods such as root‑finding, interpolation, numerical differentiation and integration and solving differential equations. Emphasises algorithm accuracy, stability and efficiency and uses computer algebra software.</t>
+          <t>DISGATE102</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DISGATE102</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
           <t>Mathematics</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3323,35 +2703,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Extends elementary calculus to multiple dimensions and differential equations, including complex‑valued functions. Uses computer algebra software to deepen analytical skills for science and data analysis applications.</t>
+          <t>DISGATE102</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DISGATE102</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3380,40 +2750,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Focuses on analysis of linear systems from an engineering perspective. Explores representations via differential equations, transfer functions, state‑space and signal‑flow diagrams and discusses applications in control, signal processing and modelling.</t>
+          <t>DISGATE102</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>DISGATE102</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
           <t>Mathematics</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3442,27 +2797,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Provides a foundation in mathematical statistics. Covers probability theory, discrete and continuous distributions, sampling, parameter estimation and simulation; uses computer algebra software to develop theoretical understanding and practical skills.</t>
+          <t>DISGATE102</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>DISGATE102</t>
+          <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3471,16 +2821,6 @@
         </is>
       </c>
       <c r="N46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3509,27 +2849,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Introduces the sustainable engineering approach of working with natural processes for flood protection, land reclamation and port development. Covers history and principles of ecosystem‑based design, explores case studies and includes guest lectures and field excursions.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
+          <t>Delta Challenges</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Delta Challenges</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3543,16 +2878,6 @@
         </is>
       </c>
       <c r="N47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3581,40 +2906,30 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Explores sustainable water management in delta regions. Focuses on adaptation to rising seas, floods and land subsidence; engages students in projects in Zeeland; and highlights nature‑based solutions and resilient infrastructure.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
           <t>Delta Challenges</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3643,35 +2958,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Examines strategies and technologies towards a circular economy. Explores resource security and stewardship, develops lab skills and inorganic chemistry knowledge, and connects to themes at the Delta Climate Center.</t>
+          <t>ENSGATE201</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ENSGATE201</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
           <t>Delta Challenges</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3700,27 +3005,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>This course examines sustainability through the lens of governance: “a process of rule-making and collective decision-making that includes both governmental and non-governmental actors in shaping public policy” (Fenger &amp; Bekkers, 2016). Taking this lens, we ask questions such as how are sustainability policies on the local, national, and international level made and enforced? Which actors represent which interests, and which are most influential? How is public opinion on sustainability shaped, and how does public opinion shape politics? What, at the end of the day, determines effective policy for sustainability? By the end of this course, you will have gained a deep appreciation of the complexity of the governance dimension of sustainability, and have developed the theoretical and practical understanding to critically assess mainstream policy decisions.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
           <t>Delta Challenges</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3734,16 +3034,6 @@
         </is>
       </c>
       <c r="O50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3772,27 +3062,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>The first part of this course introduces you to the basic conceptual tools for understanding governance and to the major fault line in tackling sustainability problems as identified by Charles Mann in “The Wizard and the Prophet”. Wizards are techno-optimists who believe humanity’s creativity can tackle each and every challenge, whilst Prophets argue that humans should take a holistic and systemic approach that calls for a drastic reduction of exploiting the earth resources in order to respect planetary boundaries.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
+          <t>Ecology</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Ecology</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3806,16 +3091,6 @@
         </is>
       </c>
       <c r="N51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3844,27 +3119,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>In the second part of the course we use Problem Based Learning to examine governance solutions to concrete sustainability challenges regarding food, freshwater, energy and climate change. We examine different policy solutions and investigate the interplay between facts, problem definition, solutions and interests. We also engage with questions related to climate justice and its distributive (who should pay), procedural (how do we decide) and recognition (are people being heard?) components.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
           <t>Ecology</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3878,16 +3148,6 @@
         </is>
       </c>
       <c r="O52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3916,27 +3176,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>In the third part, you will apply these analytical tools to a concrete sustainability case and draft a policy advice for a real stakeholder (government, business, or NGO, political party, citizen groups) that focuses on diagnosing, evaluating and proposing governance approaches to a specific sustainability question. Students are strongly encouraged to work on a regional or local problem that is related to the research agenda of the Delta Climate Center (food, energy, water) and parties that are involved in that.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
+          <t>Ecology</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Ecology</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3950,16 +3205,6 @@
         </is>
       </c>
       <c r="N53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3988,27 +3233,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Focuses on basic principles of ecology. Studies how environmental conditions affect organisms and examines ecological principles governing individuals, populations, communities and ecosystems, including ecological modelling and applied case studies.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
           <t>Ecology</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4022,16 +3262,6 @@
         </is>
       </c>
       <c r="O54" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4060,27 +3290,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Studies ecological processes in marine environments such as estuaries, rocky shores and coral reefs. Examines human impacts and includes guest lectures, lab visits, excursions and field work, culminating in an essay.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
+          <t>Ecology</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Ecology</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4094,16 +3319,6 @@
         </is>
       </c>
       <c r="N55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4132,40 +3347,30 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Discusses environmental impacts of agriculture and explores sustainable agriculture approaches such as agroecology, organic farming, conservation agriculture, precision agriculture, sustainable livestock farming, agroforestry, permaculture, crop rotation, integrated pest management and sustainable supply chains.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
           <t>Ecology</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4194,30 +3399,30 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Introduces Earth Science by focusing on interactions among the deep earth, lithosphere and hydrosphere. Highlights key cycles shaping Earth’s surface and includes indoor/outdoor labs and a multi‑day field excursion.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
+          <t>Environmental Studies</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Environmental Studies</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4246,27 +3451,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Covers geoscience principles and analytical tools to understand natural disasters. Compares risks from climate change‑driven events and mining disasters and teaches actions to reduce risks from events like earthquakes, droughts and toxic algae blooms.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
           <t>Environmental Studies</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4274,7 +3474,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4303,40 +3503,25 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Provides hands‑on experience with GIS and data integration using geospatial data from satellites and drones. Uncovers how human actions impact ecosystems and climate and promotes sustainable practices through research projects.</t>
+          <t>ENSGATE101</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ENSGATE101</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
           <t>Environmental Studies</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4365,40 +3550,25 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Explores soils and aquifers through fieldwork and lab analyses. Covers soil formation, properties, health and remediation and investigates mapping aquifers for geothermal energy, coastal defence and freshwater resource assessment.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
           <t>Environmental Studies</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4427,45 +3597,25 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Explores interactions among biosphere, hydrosphere, lithosphere and atmosphere. Teaches system modelling, uses proxies and isotope tracers to study past and future climates and includes a field trip focused on greenhouse gas pathways.</t>
+          <t>ENSGATE101</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ENSGATE101</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
           <t>Environmental Studies</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4494,27 +3644,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Investigates natural waters and their interactions with rocks, soils and minerals. Examines biogeochemical processes and cycles, including weathering, mineral formation, absorption, water treatment and resource recovery; utilises geochemical modelling and a case study.</t>
+          <t>ENSGATE101</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ENSGATE101</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
+          <t>Environmental Studies</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Environmental Studies</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4528,16 +3673,6 @@
         </is>
       </c>
       <c r="N62" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4566,35 +3701,25 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Provides in‑depth geoscience research into resource and environmental challenges such as nuclear waste storage, geothermal energy and CO₂ capture. Students conduct literature reviews and produce class reports for presentation to a professional conference.</t>
+          <t>ENSGATE201</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ENSGATE201</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
           <t>Environmental Studies</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4623,27 +3748,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Provides key concepts in physics, chemistry, materials science, mathematics and modelling necessary for sustainability. Uses a case study to connect concepts to real‑world sustainability challenges and prepares students for 200‑level sustainability courses.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Gateway</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>G</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4657,16 +3777,6 @@
         </is>
       </c>
       <c r="N64" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4695,27 +3805,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Builds on Sustainability Essentials I. Applies tools and knowledge to a real‑world sustainability case study and allows students to delve deeper into aspects connected to their field of interest.</t>
+          <t>ENSGATE101</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ENSGATE101</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
           <t>Gateway</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4729,16 +3834,6 @@
         </is>
       </c>
       <c r="O65" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4767,27 +3862,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Focuses on drivers and impacts of anthropogenic climate change on sea level, ocean acidification, ecology and society. Discusses adaptation and mitigation solutions, including renewable energy systems, carbon storage and climate‑adaptive planning, and examines climate governance and justice.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
+          <t>Sustainability</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4801,16 +3891,6 @@
         </is>
       </c>
       <c r="N66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4839,40 +3919,25 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Teaches evaluation of environmental impacts of products, processes and services throughout their lifecycle. Emphasises strategic planning for a circular economy through hands‑on learning.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
+          <t>Sustainability</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4901,40 +3966,30 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Develops skills to recognise and handle misinformation. Discusses cognitive biases and detection methods, distinguishes real from fake experts, and includes case studies and a video project tackling a misinformation topic.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
           <t>Sustainability</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4963,30 +4018,30 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Introduces renewable energy resources and technologies, discussing environmental, political and economic constraints. Covers energy storage and demand management and aims to balance energy supply and demand.</t>
+          <t>ENSGATE101</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ENSGATE101</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
+          <t>Sustainability</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5015,27 +4070,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Teaches assessment of energy usage patterns and strategies for reducing consumption or transitioning to cleaner energy. Explores solar, wind and bioenergy solutions and includes technical and economic analysis; students deliver a report and presentation to a partner company.</t>
+          <t>ENSGATE201</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ENSGATE201</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
           <t>Sustainability</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5044,16 +4094,6 @@
         </is>
       </c>
       <c r="O70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5072,60 +4112,30 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ENSSUST313</t>
+          <t>ENSSUST315</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Research in a Sustainable Delta</t>
+          <t>Spatial Planning</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>In this project course you will work in small teams of two or three students on a research problem relevant for sustainability in the broadest sense. We are looking for collaborations with local companies and other institutions. The research questions are supplied by a regional institution or company that is active in areas related to sustainability in the broadest sense. In this way it is guaranteed that the research projects are indeed relevant for the Zeeland delta. Furthermore, students will have access to expertise and/or facilities of the external partner, which will broaden their perspective. Usually, there will be one person affiliated with the external partner organization involved with a project team as external advisor</t>
+          <t>ENSGATE201</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Environment &amp; Sustainability</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
           <t>Sustainability</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5134,47 +4144,57 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ENS</t>
+          <t>GOS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SUST</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ENSSUST315</t>
+          <t>GOSGATE102</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Spatial Planning</t>
+          <t>Law, Society &amp; Justice</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Explores spatial engineering and geospatial technologies like GIS and remote sensing for addressing global challenges such as natural disasters, food shortages, resource decline and pollution. Emphasises hands‑on projects in disaster response, sustainable agriculture and environmental monitoring.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ENSGATE201</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -5186,42 +4206,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>HIST</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GOSGATE102</t>
+          <t>GOSHIST111</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Law, Society &amp; Justice</t>
+          <t>Modern History</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Examines law from legal, socio‑scientific and normative perspectives. Explores definitions, legal traditions and fields of law, investigates the relationship between law and society and the concept of justice, and includes case law, excursion to international legal organisations, interviews with practitioners and a moot court session.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
+          <t>History</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Gateway</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>G</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5235,16 +4250,6 @@
         </is>
       </c>
       <c r="N73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5263,60 +4268,45 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GOSHIST111</t>
+          <t>GOSHIST112</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Modern History</t>
+          <t>Histories of Gender</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Provides a chronological overview of history from 1815 to the present. Discusses industrialisation, popular sovereignty and national self‑determination, and covers major economic, political and cultural developments including revolutions, world wars and the fall of communism.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
+          <t>History</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5335,37 +4325,32 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GOSHIST112</t>
+          <t>GOSHIST211</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Histories of Gender</t>
+          <t>History of Empires</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Explores lives of ordinary people through the lens of gender from the 19th to 21st centuries. Uses storytelling across cultural forms; topics include slavery, mid‑20th‑century life, conversion therapy, queer cinema and banned books; engages with projects like Walking With Pride.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
+          <t>History</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5373,22 +4358,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5407,60 +4382,45 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GOSHIST211</t>
+          <t>GOSHIST213</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>History of Empires</t>
+          <t>Western Way of War</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Examines the rise and fall of empires and the contested concept of empire. Discusses oppressive and benevolent features of empires, covers key theories on empires and power politics and analyses major historical examples.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
           <t>History</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5479,37 +4439,32 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GOSHIST213</t>
+          <t>GOSHIST311</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Western Way of War</t>
+          <t>Native American Histories</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Provides a chronological overview of warfare in the Western world from antiquity to the present. Covers weapons, technology, strategy, defence, mercenaries, cavalry, chivalry, Blitzkrieg, guerrilla warfare and nuclear arsenals, illustrating competition for mastery in Western history.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
           <t>History</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5523,16 +4478,6 @@
         </is>
       </c>
       <c r="O77" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5551,37 +4496,32 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GOSHIST311</t>
+          <t>GOSHIST312</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Native American Histories</t>
+          <t>History Research Seminar</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>This course introduces students to Native American history and life from the 19th through the 21st century.  It argues that power, fear, misogyny, education, genocide, and resilience shape the Indigenous past and present. Topics we explore include the “Stolen Lives” of Indian children forcibly taken from their homes and placed in Indian Boarding Schools from the 1830’s through the 1990’s; Murdered and Missing Indigenous Women and Girls in the twenty-first century; and the individual and community forms of cultural resistance and environmental regeneration that connect past with present and future generations. We learn from the Native American scholars and 2Spirit youth that speak to and with the class. Exchange of cultural and intellectual knowledge also happens when we work with Lakota students to address contemporary challenges. Legislation, memoir, novels, and Indigenous children’s stories are central to our studies. So are the analyses of contemporary music and artistic expressions and exhibitions, as well as Hollywood and Indigenous film featuring Native American histories and lives.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
           <t>History</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5595,16 +4535,6 @@
         </is>
       </c>
       <c r="O78" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5618,65 +4548,50 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HIST</t>
+          <t>LAWJ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GOSHIST312</t>
+          <t>GOSLAWJ111</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>History Research Seminar</t>
+          <t>Human Rights: Law &amp; Philosophy</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guides students through the full arc of historical inquiry, from formulating research questions to engaging critically with sources. Emphasises methodological rigour and interdisciplinary thinking and culminates in a substantial research paper.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5695,37 +4610,32 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GOSLAWJ111</t>
+          <t>GOSLAWJ211</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Human Rights: Law &amp; Philosophy</t>
+          <t>Criminal Law &amp; Criminal Justice</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Offers a legal, historical and philosophical approach to human rights. Studies classical and modern philosophers, traces the rise of human rights, examines the US Bill of Rights and the French Declaration, and discusses human rights treaties.</t>
+          <t>GOSGATE102</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Law</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5733,22 +4643,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5767,60 +4662,45 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GOSLAWJ211</t>
+          <t>GOSLAWJ212</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Criminal Law &amp; Criminal Justice</t>
+          <t>Introduction to Public International Law</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Examines moral and legal justifications for criminalisation and punishment. Investigates guiding principles of criminal law and justice, including criminal accountability, guilt, legality and fundamental principles, and applies theory through a simulated legal aid clinic.</t>
+          <t>GOSGATE102</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>GOSGATE102</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
           <t>Law</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5839,37 +4719,32 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GOSLAWJ212</t>
+          <t>GOSLAWJ213</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Introduction to Public International Law</t>
+          <t>Comparative Constitutional Law</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Introduces rules, institutions and politics of public international law. Covers treaties, the UN, armed conflict, war crimes, refugee protection and climate change. Students analyse cases, debate issues and produce a podcast connecting law to global challenges.</t>
+          <t>GOSGATE102</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>GOSGATE102</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
           <t>Law</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5883,16 +4758,6 @@
         </is>
       </c>
       <c r="O82" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5911,60 +4776,45 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GOSLAWJ213</t>
+          <t>GOSLAWJ311</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Comparative Constitutional Law</t>
+          <t>Principles of Private Law</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Explores constitutional law and state organisation, using a comparative approach. Covers constitutionalism, separation of powers, judicial review, federalism and fundamental rights, and discusses constitution‑making, religious constitutions and constitutional backsliding.</t>
+          <t>GOSGATE102</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>GOSGATE102</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Law</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5983,60 +4833,45 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GOSLAWJ311</t>
+          <t>GOSLAWJ312</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Principles of Private Law</t>
+          <t>Foundations of European Union Law</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Examines principles of property law, tort law, contract law and other fields within private law. Uses comparisons of legal systems in four countries to explore rights and obligations arising from daily interactions.</t>
+          <t>GOSGATE102</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>GOSGATE102</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
           <t>Law</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6050,65 +4885,50 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LAWJ</t>
+          <t>PHIL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GOSLAWJ312</t>
+          <t>GOSPHIL111</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Foundations of European Union Law</t>
+          <t>Introduction to Western Philosophy</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Introduces the EU legal order. Studies institutions, framework, citizenship and the internal market using problem‑based exercises and guest lectures.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>GOSGATE102</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
+          <t>Philosophy</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Law</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6127,60 +4947,45 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GOSPHIL111</t>
+          <t>GOSPHIL212</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Introduction to Western Philosophy</t>
+          <t>Ethics</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Introduces central themes from Western philosophy over 2,500 years. Encourages inquiry into the significance of philosophical issues and their relation to other disciplines and teaches theoretical methods used by philosophers.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
           <t>Philosophy</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6199,37 +5004,32 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GOSPHIL212</t>
+          <t>GOSPHIL214</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ethics</t>
+          <t>Philosophy of Mind</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Explores theories of moral reasoning—virtue ethics, deontology, utilitarianism—and discusses moral knowledge, motivation, responsibility and the relation between happiness and pleasure. Applies theories to practical issues such as animal rights, privacy, future generations, war, punishment, disability and equality.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
           <t>Philosophy</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6243,16 +5043,6 @@
         </is>
       </c>
       <c r="O87" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6271,37 +5061,32 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GOSPHIL214</t>
+          <t>GOSPHIL311</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Philosophy of Mind</t>
+          <t>Philosophy of Emotion</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Examines historical and modern work on the philosophy of mind. Discusses Descartes’ dualism, the nature of consciousness, AI and animal minds, personal identity, transformative experiences and the influence of technology on experience.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
+          <t>Philosophy</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Philosophy</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6315,16 +5100,6 @@
         </is>
       </c>
       <c r="O88" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6343,60 +5118,40 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GOSPHIL311</t>
+          <t>GOSPHIL313</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Philosophy of Emotion</t>
+          <t>Free Will, Time &amp; the Self</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Explores emotions from a philosophical perspective. Discusses nature and rationality of emotions, their role in ethics and art, and draws on historical and contemporary sources.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="J89" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6410,42 +5165,42 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PHIL</t>
+          <t>POLI</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GOSPHIL313</t>
+          <t>GOSPOLI111</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Free Will, Time &amp; the Self</t>
+          <t>Introduction to Political Philosophy</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Investigates concepts of free will, the role of luck and openness of the future. Explores relations between free will, time and the self across multiple modules and contemporary debates.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
+          <t>Political Science</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Philosophy</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6453,7 +5208,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6472,37 +5227,32 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GOSPOLI111</t>
+          <t>GOSPOLI112</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Introduction to Political Philosophy</t>
+          <t>Foundations of Comparative Politics</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Introduces political philosophy. Examines concepts such as authority, freedom, equality, democracy, human rights, pluralism, multiculturalism, poverty and environmental issues through classical and contemporary texts. Emphasises essay writing and presentations.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
+          <t>Political Science</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Political Science</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6516,16 +5266,6 @@
         </is>
       </c>
       <c r="N91" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6544,60 +5284,45 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GOSPOLI112</t>
+          <t>GOSPOLI212</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Foundations of Comparative Politics</t>
+          <t>Theory of International Relations</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Provides analytical tools to compare political systems and democracies. Examines phenomena like democratic backsliding, decline of political parties, rise of populism, media changes, non‑majoritarian institutions and globalization’s impact on domestic politics.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
           <t>Political Science</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6616,60 +5341,45 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GOSPOLI212</t>
+          <t>GOSPOLI311</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Theory of International Relations</t>
+          <t>European Union Politics</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Introduces basic theories of international relations and applies them to contemporary issues such as climate change, energy, humanitarian intervention, global crises and international relations between North-South and South-South actors. Includes a UN Security Council negotiation simulation.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
+          <t>Political Science</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Political Science</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6688,60 +5398,35 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GOSPOLI311</t>
+          <t>GOSPOLI312</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>European Union Politics</t>
+          <t>Public Policy Analysis</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Introduces EU politics. Outlines actors, institutions and decision‑making rules; examines responses to crises; and employs various approaches to study EU politics and policy‑making.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
           <t>Political Science</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6760,37 +5445,47 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GOSPOLI312</t>
+          <t>GOSPOLI313</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Public Policy Analysis</t>
+          <t>Peace &amp; Conflict</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Investigates public policy in the context of globalization. Uses a case study on sugar to examine policy‑making phases and alternative conceptualisations across national and international arenas. Students write policy memos.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
           <t>Political Science</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -6802,65 +5497,50 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>POLI</t>
+          <t>SOCI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GOSPOLI313</t>
+          <t>GOSSOCI111</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Peace &amp; Conflict</t>
+          <t>Introduction to Sociology</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Introduces Peace &amp; Conflict Studies. Examines definitions of peace and conflict; analyzes conflict causation, violence typologies and radicalisation; applies reconciliation and conflict‑transformation models to real‑world scenarios through lectures and portfolio work.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Political Science</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6879,60 +5559,45 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GOSSOCI111</t>
+          <t>GOSSOCI212</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Introduction to Sociology</t>
+          <t>Qualitative Research Methodology</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Introduces concepts, theories and methods of sociology. Examines socio‑historical context of key authors like Marx, Weber, Durkheim and Du Bois, and encourages exploration of social problems related to race, gender and class through theoretical approaches and methodologies.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
           <t>Sociology</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6951,60 +5616,40 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GOSSOCI212</t>
+          <t>GOSSOCI214</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Qualitative Research Methodology</t>
+          <t>Modern Sociology</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Introduces qualitative research methodology. Covers designing questions, interpreting meaning and conducting small team projects, while reflecting on complexity and power dynamics in social research.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
           <t>Sociology</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7023,55 +5668,40 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GOSSOCI214</t>
+          <t>GOSSOCI215</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Modern Sociology</t>
+          <t>Social Movements &amp; Environmental Justice</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Examines the trajectory of sociology within the culture of imperialism and colonial responses. Studies leading social theories and debates about modernity and critically engages with sociological discourses.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
           <t>Sociology</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7090,45 +5720,45 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GOSSOCI215</t>
+          <t>GOSSOCI311</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Social Movements &amp; Environmental Justice</t>
+          <t>New Issues in Contemporary Social Theory</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Focuses on social movement theories and environmental justice. Uses case studies from the Environmental Justice Atlas and integrates perspectives such as feminism, anti‑colonialism, degrowth and environmental peacebuilding to encourage civic engagement.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Government &amp; Society</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sociology</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7137,47 +5767,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GOS</t>
+          <t>HCB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SOCI</t>
+          <t>BIOM</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GOSSOCI311</t>
+          <t>HCBBIOM111</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>New Issues in Contemporary Social Theory</t>
+          <t>Epidemiology &amp; Public Health</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Examines contemporary sociological debates about civil society through critical tradition, neo‑functionalism and decolonial critiques. Includes research group projects with NGOs or civil society organizations that translate conceptual insights into empirical analysis.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sociology</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>Biomedical Science</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -7191,16 +5811,6 @@
         </is>
       </c>
       <c r="N101" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7219,46 +5829,45 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HCBBIOM111</t>
+          <t>HCBBIOM211</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Epidemiology &amp; Public Health</t>
+          <t>Functional Anatomy</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Public health is about changing the world. From pandemics to lifestyle-related diseases, from screening for disease to improving water and air quality, it asks: how can we improve to keep the population healthy?_x000D_
-But how do we know what actually works? In this course you will dive into epidemiology: the science behind public health. You will learn how to study disease, risks, and changes over time, and how to critically evaluate evidence. Because behind every public health decision lies a question of evidence, and by the end of this course, you will be equipped to engage with it. This course invites you to look beyond the lab, the hospital, and the library, into the wider world where health is shaped. What matters most if we truly care about health, and how can we influence that?</t>
+          <t>HCBGATE101</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
           <t>Biomedical Science</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7277,60 +5886,45 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HCBBIOM211</t>
+          <t>HCBBIOM311</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Functional Anatomy</t>
+          <t>Pharmacology</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Introduces human body functioning using imaging, surface anatomy and dissection materials. Shows how anatomy serves function and discusses ethical considerations of learning from the dead.</t>
+          <t>HCBGATE101</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>HCBGATE101</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
+          <t>Biomedical Science</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Biomedical Science</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7349,60 +5943,45 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HCBBIOM311</t>
+          <t>HCBBIOM312</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Pharmacology</t>
+          <t>Infection &amp; Immunity</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Covers the science of drugs—their origin, composition, kinetics, therapeutic use and toxicity. Discusses drug targets, interactions and kinetics, enabling students to explain therapies in terms of molecular targets and physiological consequences.</t>
+          <t>HCBGATE101</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>HCBGATE101</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
           <t>Biomedical Science</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7421,37 +6000,32 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HCBBIOM312</t>
+          <t>HCBBIOM313</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Infection &amp; Immunity</t>
+          <t>Mechanisms of Disease</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Explores fundamental processes in immunology such as recognition of self vs non‑self, lymphocyte receptor development and innate and adaptive immune responses. Examines host‑pathogen interactions, inflammation, tissue damage and immunopathology.</t>
+          <t>HCBGATE101</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>HCBGATE101</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
           <t>Biomedical Science</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -7465,16 +6039,6 @@
         </is>
       </c>
       <c r="O105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S105" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7488,42 +6052,37 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BIOM</t>
+          <t>COGN</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HCBBIOM313</t>
+          <t>HCBCOGN112</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mechanisms of Disease</t>
+          <t>Neurobiology</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Examines molecular and cellular defects triggering pathologies. Presents clinical cases, discusses disease mechanisms and treatments across systems and includes an assignment to invent an imaginary disease.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>HCBGATE101</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Biomedical Science</t>
+          <t>Cognitive Science</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7537,16 +6096,6 @@
         </is>
       </c>
       <c r="O106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7565,39 +6114,29 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>HCBCOGN112</t>
+          <t>HCBCOGN212</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Neurobiology</t>
+          <t>Perception &amp; Action</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Examines evolution and complexity of brains. Explores animal cognition, welfare and research ethics and studies how brain regions and rhythms regulate behaviour through interactive assignments.</t>
+          <t>HCBGATE102</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
           <t>Cognitive Science</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>X</t>
@@ -7609,16 +6148,6 @@
         </is>
       </c>
       <c r="O107" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7637,55 +6166,45 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>HCBCOGN212</t>
+          <t>HCBCOGN311</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Perception &amp; Action</t>
+          <t>Higher Order Functions</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Explores neural mechanisms behind perception and action. Examines how the brain processes sensory information and guides goal‑directed behaviour using methods from cognitive neuroscience and neuropsychology.</t>
+          <t>HCBGATE102</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
+          <t>Cognitive Science</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Cognitive Science</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7704,60 +6223,30 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>HCBCOGN311</t>
+          <t>HCBCOGN312</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Higher Order Functions</t>
+          <t>Psycholinguistics</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Deepens understanding of neurophysiology and neuroanatomy. Explores higher‑level cognitive functions—memory, emotion, social cognition, executive functioning and language—and engages with current research while designing experiments.</t>
+          <t>HCBGATE102</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
           <t>Cognitive Science</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7771,50 +6260,50 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>COGN</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>HCBCOGN312</t>
+          <t>HCBGATE101</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Psycholinguistics</t>
+          <t>Foundation of Life, Health &amp; Biomedicine</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Psycholinguistics is the study of the neurobiological and psychological factors that enable us to acquire, use, and understand language. Modern research draws on cognitive psychology, neuroscience, and computer science to investigate how language is processed. The course focuses primarily, though not exclusively, on the neuroscience of language. Students examine theoretical and experimental issues in speech production and comprehension, language impairments, the relationship between thought and language, and the evolution and acquisition of language. They also gain hands-on experience with experimental approaches to the study of language and develop an understanding of human linguistic capacity as a subject of multidisciplinary research. Topics covered: What is language? Evolutionary aspects of language and animal communication; language and thought; aphasia; language acquisition; bilingualism; speech comprehension; semantics; reading and dyslexia; speech production.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Cognitive Science</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7833,37 +6322,37 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>HCBGATE101</t>
+          <t>HCBGATE102</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Foundation of Life, Health &amp; Biomedicine</t>
+          <t>Introduction to Brain &amp; Behavior</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Introduces biochemistry, macromolecules, cells, organ systems, DNA and cell function. Connects fundamentals to health and disease and serves as a starting point for medicine, biomedical science, life science or public health; no lab experience needed.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Gateway</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7871,22 +6360,27 @@
           <t>X</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr">
+      <c r="O111" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7900,46 +6394,36 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>HCBLIFE211</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Introduction to Brain &amp; Behavior</t>
+          <t>Molecular Cell Biology</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Explores why people behave as they do and how brain injuries affect mental processes. Discusses nature and nurture, introduces brain anatomy and psychological theories, and provides a gateway to cognitive science and clinical psychology.</t>
+          <t>HCBGATE101</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
+          <t>Life Science</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Gateway</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
           <t>X</t>
         </is>
       </c>
@@ -7948,42 +6432,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="O112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8002,37 +6456,32 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>HCBLIFE211</t>
+          <t>HCBLIFE212</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Molecular Cell Biology</t>
+          <t>Human Physiology</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Provides foundation for practical applications in life science. Focuses on cellular biology of eukaryotes and prokaryotes, revisits concepts from introductory courses, examines current research and encourages evaluating reproducibility and modernising methods.</t>
+          <t>HCBGATE101</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>HCBGATE101</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
+          <t>Life Science</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Life Science</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -8040,22 +6489,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S113" t="inlineStr">
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8074,37 +6513,32 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HCBLIFE212</t>
+          <t>HCBLIFE213</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Human Physiology</t>
+          <t>Biochemistry</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Studies normal functioning of the human body, covering structure‑function relationships, energy handling, homeostasis, signalling, organ systems and integration of their functions.</t>
+          <t>HCBGATE101</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>HCBGATE101</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
+          <t>Life Science</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Life Science</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -8118,16 +6552,6 @@
         </is>
       </c>
       <c r="N114" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8146,60 +6570,45 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HCBLIFE213</t>
+          <t>HCBLIFE214</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Biochemistry</t>
+          <t>Life Science Laboratory</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Explores the chemistry of life and biomolecules such as proteins, sugars, lipids and nucleic acids. Discusses metabolic pathways, the role of biomolecules in health and disease and applications in medicine, biotechnology and sustainability.</t>
+          <t>HCBGATE101</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>HCBGATE101</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
           <t>Life Science</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8218,60 +6627,45 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HCBLIFE214</t>
+          <t>HCBLIFE311</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Life Science Laboratory</t>
+          <t>Molecular Pathology &amp; Genetics</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Introduces biochemical and molecular laboratory work. Covers themes like blood, proteins, bacteria, DNA and bioinformatics and provides a foundation for clinical and biomedical research.</t>
+          <t>HCBGATE101</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HCBGATE101</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
           <t>Life Science</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S116" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8285,42 +6679,37 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>PSYC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HCBLIFE311</t>
+          <t>HCBPSYC111</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Molecular Pathology &amp; Genetics</t>
+          <t>Social Psychology</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Covers general and molecular pathology and genetics. Studies cell injury, death, inflammation, immunity, tissue repair, regeneration, fibrosis and neoplasia, examines genetic mutations and diseases, and discusses genetic testing and ethical considerations.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HCBGATE101</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Life Science</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -8328,22 +6717,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr">
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8362,60 +6741,45 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>HCBPSYC111</t>
+          <t>HCBPSYC211</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Social Psychology</t>
+          <t>Statistics &amp; Experimental Methods</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Covers main theories, findings and principles of social psychology, emphasising its scientific approach to understanding how people’s feelings, thoughts and behaviour are influenced by the presence of others.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Psychology</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S118" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8434,60 +6798,45 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HCBPSYC211</t>
+          <t>HCBPSYC212</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Statistics &amp; Experimental Methods</t>
+          <t>Abnormal Psychology</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>The course is necessary for students who want to pursue master programs in psychology and adjacent disciplines, as well as research masters in the medical domain. It is highly recommended also for all those who want to be researchers in other domains. In addition to technical training, the course emphasizes clear academic communication. It will equip you with the skills necessary to apply advanced statistical techniques to real-world research problems. With a focus on practical application through case studies and data analysis projects, You will be able to choose the appropriate statistical model for various research scenarios and address common challenges in data interpretation.</t>
+          <t>HCBGATE102</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
           <t>Psychology</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R119" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8506,60 +6855,45 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HCBPSYC212</t>
+          <t>HCBPSYC311</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Abnormal Psychology</t>
+          <t>Medical &amp; Health Psychology</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Provides a deep dive into factors shaping mental health. Teaches critical thinking, explores the bio‑psycho‑social approach and covers mental disorders, research findings and assessment techniques.</t>
+          <t>HCBGATE102</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Psychology</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S120" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8578,60 +6912,45 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HCBPSYC311</t>
+          <t>HCBPSYC312</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Medical &amp; Health Psychology</t>
+          <t>Psychodiagnostics &amp; Psychotherapies</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Uses a biopsychosocial approach to explore how biological, psychological and socio‑cultural factors influence health and illness. Covers theories, research and interventions and focuses on the role of psychological expertise in medical settings.</t>
+          <t>HCBGATE102</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
           <t>Psychology</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8650,37 +6969,32 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HCBPSYC312</t>
+          <t>HCBPSYC313</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Psychodiagnostics &amp; Psychotherapies</t>
+          <t>Advanced Research Seminar</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Introduces key theories, methods and practices in psychodiagnostics and psychotherapy. Covers psychological assessment techniques and psychotherapeutic approaches and builds practical competencies and clinical skills.</t>
+          <t>HCBGATE102</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
           <t>Psychology</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8694,16 +7008,6 @@
         </is>
       </c>
       <c r="O122" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S122" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8722,37 +7026,32 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HCBPSYC313</t>
+          <t>HCBPSYC314</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Advanced Research Seminar</t>
+          <t>Lifespan Developmental Psychology</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>This course guides you through combining results from multiple studies using systematic reviews and meta-analysis a method now essential in psychology, medicine, social science and other disciplines. Want to know what really works? Gain hands-on skills in research synthesis that inform evidence-based policy and practice. You’ll search literature, manage data, and present findings that matter. Learn to calculate effect sizes, synthesize results and assess bias using R.</t>
+          <t>HCBGATE102</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
           <t>Psychology</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8766,16 +7065,6 @@
         </is>
       </c>
       <c r="O123" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q123" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S123" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8794,60 +7083,40 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HCBPSYC314</t>
+          <t>HCBPSYC315</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Lifespan Developmental Psychology</t>
+          <t>Youth Resilience to Extremism</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Explores human development across the lifespan. Examines physical, cognitive, emotional and social changes from prenatal life to old age and develops critical thinking about factors influencing individual uniqueness.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
           <t>Psychology</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S124" t="inlineStr">
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8856,47 +7125,47 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>HCB</t>
+          <t>MCC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PSYC</t>
+          <t>COMM</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>HCBPSYC315</t>
+          <t>MCCCOMM111</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Youth Resilience to Extremism</t>
+          <t>The Art of Rhetorical Communication</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Interdisciplinary course combining psychology and other social sciences in which students will have an opportunity to participate in an actual international research project and develop evidence-based materials for youth leaders and educators aimed at strengthening young people’s resilience to radicalization by promoting democratic school culture, emotionally supportive learning environments, empathy, civic engagement, and mental well-being.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Psychology</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8904,7 +7173,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr">
+      <c r="N125" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8923,60 +7192,50 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MCCCOMM111</t>
+          <t>MCCCOMM112</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>The Art of Rhetorical Communication</t>
+          <t>Dutch</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Teaches how to craft persuasive messages, influence opinions, inspire action and connect people. Draws on historical communicators from Aristotle to Barack Obama and applies stylistic techniques to students’ own writing and speaking.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8995,41 +7254,31 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MCCCOMM112</t>
+          <t>MCCCOMM211</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Dutch</t>
+          <t>Style &amp; Meaning</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>This course aims to develop basic skills and strategies necessary to successfully handle uncomplicated oral and written communication in Dutch in a variety of social situations that you may encounter in daily life in the Netherlands. The emphasis in the course will be on speaking in Dutch in day-to-day situations on the one hand and understanding Dutch culture on the other hand. At the end of the course students can orally express and write about themselves in Dutch, who they are, describe their family background, and interact with others in a simple way.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
           <t>Communication</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
           <t>X</t>
         </is>
       </c>
@@ -9044,16 +7293,6 @@
         </is>
       </c>
       <c r="O127" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S127" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9072,39 +7311,29 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MCCCOMM211</t>
+          <t>MCCCOMM212</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Style &amp; Meaning</t>
+          <t>Communicating the Climate Crisis</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Explores how linguistic choices inform meaning and interpretation in literary and non-fiction contexts. Introduces theoretical frameworks for close reading and addresses power dynamics, obligation, uncertainty and ideological undertones in language.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="K128" t="inlineStr">
         <is>
           <t>X</t>
@@ -9116,16 +7345,6 @@
         </is>
       </c>
       <c r="O128" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S128" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9144,55 +7363,40 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MCCCOMM212</t>
+          <t>MCCCOMM213</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Communicating the Climate Crisis</t>
+          <t>Rhetoric in Action</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Examines how the climate crisis is communicated and contested. Analyzes texts, films, exhibitions, protest art, slogans and social media alongside theory and case studies, teaching students to dissect arguments and culminating in a project where students enter the debate.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
           <t>Communication</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S129" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9211,60 +7415,45 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MCCCOMM213</t>
+          <t>MCCCOMM311</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Rhetoric in Action</t>
+          <t>Persuasive Communication</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Develops persuasive speaking skills by applying rhetorical theory in the real world. Students work with local primary school children, building public-speaking skills and empowering them to find their voices.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S130" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9283,60 +7472,45 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MCCCOMM311</t>
+          <t>MCCCOMM312</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Persuasive Communication</t>
+          <t>Creative Communication Laboratory</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Explores ethical persuasion and climate communication. Students learn persuasive communication models and frameworks and collaborate with climate scientists at the Delta Climate Centre to produce sustainability messaging on water, food and energy.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
           <t>Communication</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R131" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9350,65 +7524,50 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>COMM</t>
+          <t>HEAM</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MCCCOMM312</t>
+          <t>MCCHEAM111</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Creative Communication Laboratory</t>
+          <t>Introduction to Western Art History</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Explores meaning-making through creative expression. Students study and practice poetic forms, experiment with sonic poetry, performance and other unconventional forms of communication, engage with theoretical texts and produce their own creative work.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
+          <t>Cultural Heritage</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S132" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9427,60 +7586,45 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MCCHEAM111</t>
+          <t>MCCHEAM112</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Introduction to Western Art History</t>
+          <t>Introduction to World Archaeology</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Provides an introduction to Western art history, tracing major artistic movements from the late Middle Ages to the present. Through close study of key paintings and their makers, students gain insight into evolving styles, techniques and cultural influences.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
           <t>Cultural Heritage</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R133" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9499,60 +7643,35 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MCCHEAM112</t>
+          <t>MCCHEAM211</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Introduction to World Archaeology</t>
+          <t>African Art &amp; Heritage</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Explores ancient craft production from around the world. Examines how making objects shaped human development and how ancient solutions can inform modern sustainability.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
           <t>Cultural Heritage</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
           <t>X</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9571,50 +7690,40 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MCCHEAM211</t>
+          <t>MCCHEAM212</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>African Art &amp; Heritage</t>
+          <t>Renaissance Italy &amp; Global Mediterranean</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Examines the artistic, historical and ethical dimensions of African art. Highlights distinct forms and cultural significance, considers influence on Western modernism and addresses looting, colonial-era acquisitions and repatriation efforts.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
           <t>Cultural Heritage</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="K135" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="O135" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9633,37 +7742,32 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MCCHEAM212</t>
+          <t>MCCHEAM213</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Renaissance Italy &amp; Global Mediterranean</t>
+          <t>Greek Archaeology</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>This course examines the painting, sculpture, and architecture of Renaissance Italy and the extensive artistic connections that linked the Italian peninsula to other regions of the world. By exploring a range of geographical contexts, from the Islamic courts of the Eastern Mediterranean and the commercial routes connecting Europe, Asia, and Africa to the newly encountered territories of the Americas, students will examine how trade, colonization, and cross-cultural exchange shaped the production and meaning of Renaissance art.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
           <t>Cultural Heritage</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -9671,7 +7775,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q136" t="inlineStr">
+      <c r="O136" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9690,55 +7794,45 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MCCHEAM213</t>
+          <t>MCCHEAM312</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Greek Archaeology</t>
+          <t>Modern Art &amp; Modern Museums</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Explores the archaeology of community and democracy in early-democratic Greece, seeking ancient lessons on community decision-making.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
+          <t>Cultural Heritage</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Cultural Heritage</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9757,39 +7851,29 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MCCHEAM312</t>
+          <t>MCCHEAM315</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Modern Art &amp; Modern Museums</t>
+          <t>Heritage &amp; Ancient Democracy</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Examines debates on modern art through various themes. Focuses on the relationship between art and its presentation in museums and exhibitions, exploring curatorial practices and exhibition strategies.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
           <t>Cultural Heritage</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="J138" t="inlineStr">
         <is>
           <t>X</t>
@@ -9801,16 +7885,6 @@
         </is>
       </c>
       <c r="N138" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9829,47 +7903,35 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MCCHEAM315</t>
+          <t>MCCHEAM316</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Heritage &amp; Ancient Democracy</t>
+          <t>Writing Art's Histories</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>In the modern world democracy is associated with participation, rationality and freedom. In this course, we go back to the roots of democracy in ancient Greece, when to a modern observer, it was not very democratic at all: foreigners, slaves and women were excluded from elections and political decision-making. Even so, the inclusion of all classes, also the poor, in politics was after antiquity not achieved until the mid-nineteenth century._x000D_
-Ancient commentators criticised Athenian democracy for being too extreme just because of this broad inclusion. They argued that many were too uneducated, too emotional, and too irrational to see through the cheap play on emotions by demagogues and would-be tyrants._x000D_
-This course investigates how Athenian democracy was built, how it was intertwined with myth and religion, and expressed in art, literature and architecture. It traces the loci of democracy in archaeology, and analyses its temporary collapse in the crisis of the late fifth century BC. Most importantly, we put ourselves in our socio-political ancestors’ shoes by engaging in a simulation of the Athenian assembly, in which we have to make decisions that will change our lives forever. In doing so, we use the ancient heritage of democracy for an experiment in applied sociology – to not only understand, but to feel the meaning of political decision-making.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
           <t>Cultural Heritage</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P139" t="inlineStr">
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9883,50 +7945,50 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>HEAM</t>
+          <t>LITR</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MCCHEAM316</t>
+          <t>MCCLITR111</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Writing Art's Histories</t>
+          <t>Introduction to Literary Studies</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>This course examines the history of art history as an academic discipline, tracing how scholars have understood and interpreted art from the sixteenth century to the present. Through critical readings of influential texts by figures such as Aby Warburg, Erwin Panofsky, Ernst Gombrich, Michel Foucault, and Jacques Derrida, students explore the major ideas and methodologies that have shaped the field. Topics include art and history, aesthetics, meaning and interpretation, authorship and identity, and the challenges of art history in a globalized world.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
+          <t>Literature</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Cultural Heritage</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q140" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -9945,60 +8007,45 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MCCLITR111</t>
+          <t>MCCLITR112</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Introduction to Literary Studies</t>
+          <t>Great Literary Works</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Introduces what literature is, why we read it and how to interpret it. Covers fiction, poetry, drama, non‑fiction and film narration, exploring various literary forms and genres such as graphic narratives and romance novels.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
           <t>Literature</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -10017,60 +8064,45 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MCCLITR112</t>
+          <t>MCCLITR211</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Great Literary Works</t>
+          <t>World Myth &amp; Literature</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Provides a chronological overview of literature from the epic of Gilgamesh to post‑modernity. Reads literary and critical texts that explore human experience and teaches how to approach literature’s ambiguities and trace themes across ages.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
+          <t>Literature</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Literature</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S142" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -10089,60 +8121,45 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MCCLITR211</t>
+          <t>MCCLITR212</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>World Myth &amp; Literature</t>
+          <t>Life &amp; Travel Writing</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Investigates myths from around the world—from Gilgamesh to the Ramayana, Greek and Norse myths. Explores how myths underpin literature and connects them to contemporary global cultures.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
           <t>Literature</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -10161,60 +8178,45 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MCCLITR212</t>
+          <t>MCCLITR311</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Life &amp; Travel Writing</t>
+          <t>Film &amp; Text</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Examines autobiographical and travel writing. Explores how individuals write about self, identity and bodily experience; discusses tropes and models used to represent human experience; and considers memory and imagination in writing.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
+          <t>Literature</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Literature</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S144" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -10233,60 +8235,40 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MCCLITR311</t>
+          <t>MCCLITR312</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Film &amp; Text</t>
+          <t>Perspectives on Literary Meaning</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Studies complex links between literary and film narratives. Analyzes formal aspects of both media, discusses adaptation, intertextuality, viewer participation and narrative dynamics, and allows students to research topics like literature‑to‑film adaptation and cross‑cultural themes.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr">
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -10300,50 +8282,50 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LITR</t>
+          <t>MEDI</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MCCLITR312</t>
+          <t>MCCMEDI111</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Perspectives on Literary Meaning</t>
+          <t>Introduction to Film &amp; Media</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Examines how different perspectives—humanist, feminist, Marxist, cultural minority and psychoanalytic—affect reading and interpretation. Students undertake a research project applying selected perspectives to texts.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Literature</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q146" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -10362,37 +8344,32 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MCCMEDI111</t>
+          <t>MCCMEDI112</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Introduction to Film &amp; Media</t>
+          <t>Media Archaeology</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Introduces film and media as systems of meaning and cultural production. Examines how images, narratives and technologies shape perception, identity and power; covers film storytelling, representation and genres; and develops critical engagement skills.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -10406,16 +8383,6 @@
         </is>
       </c>
       <c r="N147" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -10434,60 +8401,40 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MCCMEDI112</t>
+          <t>MCCMEDI211</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Media Archaeology</t>
+          <t>From T.V. to TikTok</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Explores media technologies before digital culture. Studies cassette tapes, typewriters and early printing as material objects that carry meaning; includes hands‑on experiments; no technical background required.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
           <t>Media</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -10506,37 +8453,32 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MCCMEDI211</t>
+          <t>MCCMEDI212</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>From T.V. to TikTok</t>
+          <t>Media &amp; the Environment</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Explores how media shape attitudes and provide answers through examples from TV and TikTok. Examines messages that teach fear, pity, admiration and allyship.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
           <t>Media</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -10544,12 +8486,12 @@
           <t>X</t>
         </is>
       </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="O149" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -10568,60 +8510,45 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MCCMEDI212</t>
+          <t>MCCMEDI311</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Media &amp; the Environment</t>
+          <t>Media &amp; Race</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Examines representation of environmental concerns through visual culture. Explores the Anthropocene, animal representation, deep time, biocentrism, contested nature, indigenous and postcolonial media; analyzes how media shape environmental understanding; and includes a paper or media project.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S150" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -10640,132 +8567,45 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MCCMEDI311</t>
+          <t>MCCMEDI312</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Media &amp; Race</t>
+          <t>The Documentary</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Investigates storytelling and power in relation to race. Examines Afrofuturism and systemic racism and guides students in creating podcasts that explore links between past and present.</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
           <t>Media</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>MCC</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>MEDI</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>MCCMEDI312</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>The Documentary</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Introduces development of the documentary form. Students write a theoretical paper and produce a short documentary film, fostering understanding of documentary diversity and providing analytical tools for documentary study.</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="S152" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
         <is>
           <t>X</t>
         </is>

--- a/data/reference/ucr_courses.xlsx
+++ b/data/reference/ucr_courses.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O151"/>
+  <dimension ref="A1:P148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -372,60 +372,65 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>description2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>preq1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>deplabel</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tracklabel</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>2025h2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2026h1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>2026h2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>2027h1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>2027h2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>2028h1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>2028h2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>2029h1</t>
         </is>
@@ -449,30 +454,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>This course is a first-year requirement and aims to stimulate personal development, namely, being able to actively, consciously and ethically orientate oneself in relation to others and the world. It supports the development of core personal and academic skills that enhance critical thinking and independent learning. It seeks to improve and develop academic writing and presenting skills and helps students develop the foundational skills and attitudes to reflect on societal issues and engage with societal partners.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Personal &amp; Professional Development</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Academic Core</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Personal &amp; Professional Development</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -498,6 +503,11 @@
         </is>
       </c>
       <c r="O2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -521,35 +531,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>This course describes the most widely accepted accounting theory and practice with an emphasis on using and analyzing the information in financial statements. Students learn how to comprehend a typical corporate annual report and to use accounting as a tool in understanding how economic events affect business.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Accounting &amp; Corporate Finance</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -573,35 +588,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>This course examines how organizations are structured and evolve over time. It explores how organizational design relates to strategy, external environment, human behavior, culture, governance and performance. A particular emphasis is put on discussing the concept and enabling capabilities of organizational agility required to navigate a fast-paced world and tackle increased uncertainty.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Business &amp; Economy in the Age of AI</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -625,30 +645,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Businesses and entrepreneurs are confronted with legal complexity not only at the domestic level but particularly across divergent legal systems. This course presents a survey of the most essential fields of business law: contracts law, company law, trade law, intellectual property, and dispute resolution. An ultimate aim of the course is to critically examine the impact of globalization and digitization on the development of business law.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Transnational Business Law</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>BENGATE101</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -672,35 +697,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>This course develops practical financial decision-making skills through case studies and real-world applications. Students learn to analyze financial data, assess risks, and make informed investment, budgeting, and business decisions that enhance value, financial security, and long-term planning.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Money, Banking &amp; Finance</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>BENGATE101</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -719,35 +749,50 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BENECON111</t>
+          <t>BENECON211</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Introduction to Economics</t>
+          <t>Study the economy as a whole through topics such as national income, economic growth, inflation, and unemployment. Understand how governments and central banks use fiscal and monetary policies to influence economic performance over time. The course also explores business cycles, international trade, and economic crises, preparing students to evaluate policy debates and global economic trends.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>International Macroeconomics</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>BENGATE102</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -766,34 +811,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BENECON211</t>
+          <t>BENECON212</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>International Macroeconomics</t>
+          <t>Study how consumers and producers make decisions under scarcity. Explore key concepts such as rational choice, decision-making under uncertainty, and non-egoistic preferences. Analyze market structures, strategic interactions, and factor markets. Learn how markets function and examine the impact of regulation. Develop analytical tools to better understand behavior and engage with empirical research.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Microeconomics &amp; Behavior</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>BENGATE102</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>X</t>
@@ -805,6 +850,11 @@
         </is>
       </c>
       <c r="N8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -823,45 +873,40 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BENECON212</t>
+          <t>BENECON311</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Microeconomics &amp; Behavior</t>
+          <t>Investigate the role of government in the economy, focusing on how public policy influences efficiency and equity. The course covers taxation, public goods, externalities, and government spending. Combining theoretical models with empirical evidence, it evaluates how different policies affect societal welfare.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Public Economics</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>BENGATE102</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -880,35 +925,40 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BENECON311</t>
+          <t>BENECON312</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Public Economics</t>
+          <t>Econometrics supplies tools to analyze data to answer questions of causality and prediction. In this course you learn three estimators—Ordinary Least Squares, Generalized Least Squares, and Instrumental Variables—and three tests—t-test, F-test, and LM-test. Understanding the basic rules of econometrics, particularly the sampling distribution concept, is key, and the course uses Monte Carlo simulations in Stata to visualize it. Tools are applied to estimate economic relationships and make predictions, and students write an empirical paper.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Econometrics</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>BENGATE102</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -927,30 +977,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BENECON312</t>
+          <t>BENECON314</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Econometrics</t>
+          <t>This course integrates insights from psychology into economic theory to better understand how people make decisions. Learn how actual behavior deviates from the predictions of traditional economic models due to biases, heuristics, and framing. Through experiments, students will deepen their understanding of decision-making and its implications for economic theory and practice.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Behavioral Economics</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>BENGATE102</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -969,32 +1029,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>ENTR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BENECON314</t>
+          <t>BENENTR111</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Behavioral Economics</t>
+          <t>You will learn how to function in a ‘real-world’ design and development team for consumer products. We go through the phases of design and development: probe customer needs, translate these into a product concept, develop a fabrication method, analyze sustainability, analyze costs and proceeds. Design and development involves interviewing customers, brainstorming, laboratory experiments, quantitative modeling, constructing a prototype, and considering protection of intellectual property.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BENGATE102</t>
+          <t>Consumer Product Design</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Economics</t>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1002,12 +1072,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1026,40 +1091,50 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BENENTR111</t>
+          <t>BENENTR211</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Consumer Product Design</t>
+          <t>This course unpacks what drives consumer engagement with brands and how marketers build customer trust responsibly. It introduces key marketing concepts, consumer psychology, AI/technology-driven marketing innovation, and brand and communication strategies. Students will explore real-life case studies, develop a strategic marketing plan and learn how marketers build sustainable brand strategies.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Marketing &amp; Consumer Engagement</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>BENGATE102</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Entrepreneurship</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1078,45 +1153,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BENENTR211</t>
+          <t>BENENTR212</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Marketing &amp; Consumer Engagement</t>
+          <t>The course explores how companies develop strategies and drive responsible digital transformation amid rapid technology change impacting the economy and society. Students develop a strategic plan, from vision to execution, and identify digital value opportunities. Using industry cases, they gain foresight into digital technologies and their impact on strategy, business models and social responsibilities.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BENGATE102</t>
+          <t>Strategy &amp; Digital Transformation</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>BENGATE101</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Entrepreneurship</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1135,40 +1210,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BENENTR212</t>
+          <t>BENENTR311</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Strategy &amp; Digital Transformation</t>
+          <t>See how companies figure out what customers love and what they don’t. You’ll plan and carry out real research, analyze what you find, and share your results. Our course shows you how to gather opinions and turn them into smart business ideas—perfect for future marketers, analysts, or entrepreneurs.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Market Research</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>BENGATE101</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Entrepreneurship</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1187,25 +1267,30 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BENENTR311</t>
+          <t>BENENTR312</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Market Research</t>
+          <t>This course examines the institutional, political and cultural forces shaping global businesses. It first explores how international companies operate, then centers on key global challenges including cross-border governance, corporate responsibility, geopolitical strategies and global trade. It provides a comprehensive understanding of today’s complex international business environment.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>International Business &amp; Governance</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>BENGATE101</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Entrepreneurship</t>
         </is>
@@ -1234,45 +1319,55 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ENTR</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BENENTR312</t>
+          <t>BENGATE101</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>International Business &amp; Governance</t>
+          <t>Through experiential learning, students turn their own bold ideas into new ventures. No prior business expertise is required as teams work on a startup project from ideation to final pitch while gaining business and entrepreneurial skills in areas such as design thinking, business model and customer validation. The class fosters creativity and collaboration to drive business and social innovation.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BENGATE101</t>
+          <t>Entrepreneurship &amp; Business Foundations</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Entrepreneurship</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1291,34 +1386,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BENGATE101</t>
+          <t>BENGATE102</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Entrepreneurship &amp; Business Foundations</t>
+          <t>Research Methods &amp; Statistics gives you a strong foundation in how business management—and social and behavioral sciences—move from mere practices to true fields of scientific study. You’ll learn how to plan research logically, from designing studies to working with real data using experimental and survey techniques. You’ll also study descriptive and inferential statistics, with a brief intro to multivariate tools.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Research Methods &amp; Statistics</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Gateway</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>X</t>
@@ -1330,6 +1425,11 @@
         </is>
       </c>
       <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1343,32 +1443,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>LEAD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BENGATE102</t>
+          <t>BENLEAD111</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Research Methods &amp; Statistics</t>
+          <t>Personal Leadership provides a comprehensive introduction to leadership theory and practice, designed to help students discover their unique leadership style through self-awareness and practical skill-building. Through interactive workshops, reflective exercises, and real-world applications, students engage deeply with core leadership principles and develop the tools needed to lead confidently in any setting.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Personal Leadership</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Gateway</t>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1405,34 +1510,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BENLEAD111</t>
+          <t>BENLEAD112</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Personal Leadership</t>
+          <t>This course blends theory with practice from both fiction and the real world, helping you develop essential leadership skills. Learn how to inspire teams, sharpen your communication, take ethical decisions, and lead with confidence.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Leadership Communication</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Leadership</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>X</t>
@@ -1444,6 +1549,11 @@
         </is>
       </c>
       <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1462,45 +1572,45 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BENLEAD112</t>
+          <t>BENLEAD211</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Leadership Communication</t>
+          <t>Leadership &amp; Diversity Management explores how diverse perspectives and experiences shape effective leadership in dynamic, varied environments. Blending cutting-edge theories with hands-on practice, students develop the skills to lead with empathy, inclusivity, and adaptability. Through engaging case studies, interactive workshops, and reflective assessments, participants build awareness of diversity and learn to inspire ethical, collaborative teams.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Leadership &amp; Diversity Management</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>BENGATE102</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Leadership</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1519,27 +1629,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BENLEAD211</t>
+          <t>BENLEAD311</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Leadership &amp; Diversity Management</t>
+          <t>This course offers Liberal Arts and Sciences students a deep dive into the psychological, social, and structural dynamics that shape workplaces. Through interactive case discussions, simulations, and real-world insights, students develop critical skills in motivation, leadership, group dynamics, and culture. By synthesizing research and applying theory to practice, participants gain the tools to navigate and influence diverse organizational environments effectively.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Psychology of Organizations &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>BENGATE102</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Leadership</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1571,40 +1691,35 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BENLEAD311</t>
+          <t>BENLEAD312</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Psychology of Organizations &amp; Leadership</t>
+          <t>How do you get to yes? In this course you will learn how to craft persuasive arguments, deploy the right language, negotiate more effectively, and influence decisions with confidence—whether in business, leadership, or life.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Negotiation &amp; Strategic Thinking</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>BENGATE102</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Business &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Leadership</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1618,45 +1733,60 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LEAD</t>
+          <t>ARIN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BENLEAD312</t>
+          <t>DISARIN111</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Negotiation &amp; Strategic Thinking</t>
+          <t>Explores philosophical foundations and implications of AI. Examines the history of AI, ethical issues like interpretability, bias and alignment, debates about AI consciousness and implications for human nature.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BENGATE102</t>
+          <t>AI Ethics</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Business &amp; Entrepreneurship</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leadership</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+          <t>Data Science &amp; Intelligent Systems</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1675,40 +1805,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DISARIN111</t>
+          <t>DISARIN211</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AI Ethics</t>
+          <t>Introduces planning techniques for AI systems in deterministic and non‑deterministic environments. Addresses uncertainty, partial observability, resource planning and optimizing behaviour under constraints.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Decision-making in AI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>DISGATE101</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1732,35 +1857,45 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DISARIN211</t>
+          <t>DISARIN212</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Decision-making in AI</t>
+          <t>Focuses on mathematics of decision‑making, covering topics in discrete mathematics such as logic, patterns and structures, with applications to computer science and algorithm construction.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DISGATE101</t>
+          <t>Logic &amp; Discrete Mathematics</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1779,25 +1914,30 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DISARIN212</t>
+          <t>DISARIN311</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Logic &amp; Discrete Mathematics</t>
+          <t>Covers computational methods for search problems in complex and adversarial environments. Includes uninformed and informed search, local and global search, adversarial games and constraint satisfaction problems.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Optimization Methods in AI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>DISGATE101</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Artificial Intelligence</t>
         </is>
@@ -1812,7 +1952,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1831,40 +1971,40 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DISARIN311</t>
+          <t>DISARIN312</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Optimization Methods in AI</t>
+          <t>Explores reinforcement learning. Covers theoretical frameworks and algorithms and requires students to implement algorithms and build agents using neural networks that learn through trial and error.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>DISGATE101</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1878,35 +2018,45 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ARIN</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DISARIN312</t>
+          <t>DISCOMP211</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Reinforcement Learning</t>
+          <t>Introduces computer networks and operating systems. Covers how the internet works and the role of an OS in resource management and application support.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>Networks &amp; Operating Systems</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>DISGATE101</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1930,40 +2080,45 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DISCOMP211</t>
+          <t>DISCOMP212</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Networks &amp; Operating Systems</t>
+          <t>Introduces relational database management systems and SQL. Covers relational database theory, authorization, normalization and query processing.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DISGATE101</t>
+          <t>Database Management Systems</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1982,40 +2137,40 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DISCOMP212</t>
+          <t>DISCOMP213</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Database Management Systems</t>
+          <t>Covers software design, creation, testing and maintenance. Uses C++ and Haskell and covers planning, requirements gathering, testing, deployment and maintenance through discussions and code reviews.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Software Development</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>DISGATE101</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2034,25 +2189,30 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DISCOMP213</t>
+          <t>DISCOMP311</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Software Development</t>
+          <t>Teaches design and analysis of algorithms and data structures, emphasizing performance analysis and focusing on prominent algorithms and data structures.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Algorithms &amp; Data Structures</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>DISGATE101</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
@@ -2062,7 +2222,17 @@
           <t>X</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2081,40 +2251,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DISCOMP311</t>
+          <t>DISCOMP312</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Algorithms &amp; Data Structures</t>
+          <t>Studies modern algebraic algorithms and optimization methods. Emphasises algorithmic thinking and mathematical modelling of computational problems.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>Advanced Algorithms</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>DISGATE101</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2133,32 +2298,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DISCOMP312</t>
+          <t>DISDATA111</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Advanced Algorithms</t>
+          <t>Develops foundational skills in data visualization, cleaning and manipulation. Explores spatial and text data and includes hands‑on work with datasets from various disciplines.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DISGATE101</t>
+          <t>Introduction to Data Science</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2166,7 +2336,37 @@
           <t>X</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2185,60 +2385,45 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DISDATA111</t>
+          <t>DISDATA211</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Introduction to Data Science</t>
+          <t>Covers core machine learning techniques from linear regression to advanced tree‑based methods. Discusses strengths and weaknesses and applies methods to real data from fields like medicine, physics and economics.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Data Science</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="M35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2262,35 +2447,35 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DISDATA211</t>
+          <t>DISDATA212</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Covers processing and analysis of image data, including feature detection and tracking. Discusses applications in medicine, self‑driving vehicles, gaming, robotics and traffic management.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>Image Processing &amp; Computer Vision</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Data Science</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2300,7 +2485,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2319,40 +2504,45 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DISDATA212</t>
+          <t>DISDATA311</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Image Processing &amp; Computer Vision</t>
+          <t>Explores theory and practice of neural networks. Students build basic networks and progress to complex networks for computer vision, and discuss recent developments in large language and image generation models.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Neural Networks &amp; Deep Learning</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>DISGATE102</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Data Science</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2371,40 +2561,40 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DISDATA311</t>
+          <t>DISDATA312</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Neural Networks &amp; Deep Learning</t>
+          <t>Covers computational problems in robotics. Includes forward and inverse kinematics, motion planning, collision avoidance and robotic grasping and manipulation.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>Robotics</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>DISGATE102</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Data Science</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2418,32 +2608,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DISDATA312</t>
+          <t>DISGATE101</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Introduces programming and computer science. Covers structured programming, data constructs, testing, debugging and object‑oriented programming with Python, and develops computational problem‑solving skills.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DISGATE102</t>
+          <t>Introduction to Programming</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Data Science</t>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2451,7 +2646,17 @@
           <t>X</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2470,35 +2675,35 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DISGATE101</t>
+          <t>DISGATE102</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Introduction to Programming</t>
+          <t>Introduces linear algebra (vectors, matrices, eigenvalues) and calculus (limits, differentiation, integration) to construct and solve equations. Provides problem‑solving skills applicable across disciplines.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>Mathematical Methods</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Gateway</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2509,6 +2714,11 @@
         </is>
       </c>
       <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2522,35 +2732,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>MATH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>DISMATH211</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Introduces systems of equations, vectors, matrices and linear spaces with emphasis on visual and conceptual understanding. Applies concepts across fields and includes hands‑on exercises using computer algebra software.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Linear Algebra</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>DISGATE102</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Mathematical Methods</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Gateway</t>
-        </is>
-      </c>
       <c r="H41" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2584,45 +2799,45 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DISMATH211</t>
+          <t>DISMATH213</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Introduces numerical methods such as root‑finding, interpolation, numerical differentiation and integration and solving differential equations. Emphasises algorithm accuracy, stability and efficiency and uses computer algebra software.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>Computational &amp; Numerical Methods</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>DISGATE102</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2641,40 +2856,40 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DISMATH213</t>
+          <t>DISMATH214</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Computational &amp; Numerical Methods</t>
+          <t>Extends elementary calculus to multiple dimensions and differential equations, including complex‑valued functions. Uses computer algebra software to deepen analytical skills for science and data analysis applications.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>Advanced Calculus</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>DISGATE102</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2693,35 +2908,40 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DISMATH214</t>
+          <t>DISMATH312</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Advanced Calculus</t>
+          <t>Focuses on analysis of linear systems from an engineering perspective. Explores representations via differential equations, transfer functions, state‑space and signal‑flow diagrams and discusses applications in control, signal processing and modelling.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>Linear Systems</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>DISGATE102</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2740,35 +2960,45 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DISMATH312</t>
+          <t>DISMATH314</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Linear Systems</t>
+          <t>Provides a foundation in mathematical statistics. Covers probability theory, discrete and continuous distributions, sampling, parameter estimation and simulation; uses computer algebra software to develop theoretical understanding and practical skills.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>Probability &amp; Statistics</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>DISGATE102</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Data Science &amp; Intelligent Systems</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2777,50 +3007,60 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>ENS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MATH</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DISMATH314</t>
+          <t>ENSDELT111</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Probability &amp; Statistics</t>
+          <t>Introduces the sustainable engineering approach of working with natural processes for flood protection, land reclamation and port development. Covers history and principles of ecosystem‑based design, explores case studies and includes guest lectures and field excursions.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>DISGATE102</t>
+          <t>Building with Nature</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Data Science &amp; Intelligent Systems</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
+          <t>Environment &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Delta Challenges</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2839,45 +3079,45 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ENSDELT111</t>
+          <t>ENSDELT211</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Building with Nature</t>
+          <t>Explores sustainable water management in delta regions. Focuses on adaptation to rising seas, floods and land subsidence; engages students in projects in Zeeland; and highlights nature‑based solutions and resilient infrastructure.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Living with Water</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Delta Challenges</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2896,35 +3136,35 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ENSDELT211</t>
+          <t>ENSDELT311</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Living with Water</t>
+          <t>Examines strategies and technologies towards a circular economy. Explores resource security and stewardship, develops lab skills and inorganic chemistry knowledge, and connects to themes at the Delta Climate Center.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>R3: Recycling, Recovery, Remediation</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>ENSGATE201</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Delta Challenges</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2948,25 +3188,30 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ENSDELT311</t>
+          <t>ENSDELT312</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R3: Recycling, Recovery, Remediation</t>
+          <t>This course examines sustainability through the lens of governance: “a process of rule-making and collective decision-making that includes both governmental and non-governmental actors in shaping public policy” (Fenger &amp; Bekkers, 2016). Taking this lens, we ask questions such as how are sustainability policies on the local, national, and international level made and enforced? Which actors represent which interests, and which are most influential? How is public opinion on sustainability shaped, and how does public opinion shape politics? What, at the end of the day, determines effective policy for sustainability? By the end of this course, you will have gained a deep appreciation of the complexity of the governance dimension of sustainability, and have developed the theoretical and practical understanding to critically assess mainstream policy decisions.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ENSGATE201</t>
+          <t>Governance of Sustainability</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Delta Challenges</t>
         </is>
@@ -2976,7 +3221,17 @@
           <t>X</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2990,32 +3245,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ECOL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ENSDELT312</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Governance of Sustainability</t>
+          <t>ENSECOL111</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>Introduction to Biodiversity</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Delta Challenges</t>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Ecology</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3052,34 +3307,29 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ENSECOL111</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Introduction to Biodiversity</t>
+          <t>ENSECOL112</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>Conservation Biology</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Ecology</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>X</t>
@@ -3091,6 +3341,11 @@
         </is>
       </c>
       <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3109,25 +3364,25 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ENSECOL112</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Conservation Biology</t>
+          <t>ENSECOL211</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>The Science of Evolution</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>Ecology</t>
         </is>
@@ -3166,34 +3421,34 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ENSECOL211</t>
+          <t>ENSECOL212</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>The Science of Evolution</t>
+          <t>Focuses on basic principles of ecology. Studies how environmental conditions affect organisms and examines ecological principles governing individuals, populations, communities and ecosystems, including ecological modelling and applied case studies.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>Ecosystems Uncovered: How Nature Works</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Ecology</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>X</t>
@@ -3205,6 +3460,11 @@
         </is>
       </c>
       <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3223,25 +3483,30 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ENSECOL212</t>
+          <t>ENSECOL311</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ecosystems Uncovered: How Nature Works</t>
+          <t>Studies ecological processes in marine environments such as estuaries, rocky shores and coral reefs. Examines human impacts and includes guest lectures, lab visits, excursions and field work, culminating in an essay.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>Marine Biology</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Ecology</t>
         </is>
@@ -3280,45 +3545,45 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ENSECOL311</t>
+          <t>ENSECOL312</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Marine Biology</t>
+          <t>Discusses environmental impacts of agriculture and explores sustainable agriculture approaches such as agroecology, organic farming, conservation agriculture, precision agriculture, sustainable livestock farming, agroforestry, permaculture, crop rotation, integrated pest management and sustainable supply chains.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>Sustainable Farming &amp; Innovation</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Ecology</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3332,32 +3597,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ECOL</t>
+          <t>ENVI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ENSECOL312</t>
+          <t>ENSENVI111</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sustainable Farming &amp; Innovation</t>
+          <t>Introduces Earth Science by focusing on interactions among the deep earth, lithosphere and hydrosphere. Highlights key cycles shaping Earth’s surface and includes indoor/outdoor labs and a multi‑day field excursion.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>Dynamic Earth</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Ecology</t>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Environmental Studies</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3389,40 +3659,45 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ENSENVI111</t>
+          <t>ENSENVI112</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Dynamic Earth</t>
+          <t>Covers geoscience principles and analytical tools to understand natural disasters. Compares risks from climate change‑driven events and mining disasters and teaches actions to reduce risks from events like earthquakes, droughts and toxic algae blooms.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>Natural Hazards, Risks &amp; Adaptations</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Environmental Studies</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3441,40 +3716,40 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ENSENVI112</t>
+          <t>ENSENVI211</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Natural Hazards, Risks &amp; Adaptations</t>
+          <t>Provides hands‑on experience with GIS and data integration using geospatial data from satellites and drones. Uncovers how human actions impact ecosystems and climate and promotes sustainable practices through research projects.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Earth Observation</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>ENSGATE101</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Environmental Studies</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3493,35 +3768,40 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ENSENVI211</t>
+          <t>ENSENVI212</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Earth Observation</t>
+          <t>Explores soils and aquifers through fieldwork and lab analyses. Covers soil formation, properties, health and remediation and investigates mapping aquifers for geothermal energy, coastal defence and freshwater resource assessment.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ENSGATE101</t>
+          <t>Soils &amp; Aquifers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Environmental Studies</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3540,35 +3820,40 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ENSENVI212</t>
+          <t>ENSENVI213</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Soils &amp; Aquifers</t>
+          <t>Explores interactions among biosphere, hydrosphere, lithosphere and atmosphere. Teaches system modelling, uses proxies and isotope tracers to study past and future climates and includes a field trip focused on greenhouse gas pathways.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Earth System Science Tools</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>ENSGATE101</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Environmental Studies</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3587,30 +3872,45 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ENSENVI213</t>
+          <t>ENSENVI311</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Earth System Science Tools</t>
+          <t>Investigates natural waters and their interactions with rocks, soils and minerals. Examines biogeochemical processes and cycles, including weathering, mineral formation, absorption, water treatment and resource recovery; utilises geochemical modelling and a case study.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>Environmental Biogeochemistry</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>ENSGATE101</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Environmental Studies</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3634,45 +3934,40 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ENSENVI311</t>
+          <t>ENSENVI312</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Environmental Biogeochemistry</t>
+          <t>Provides in‑depth geoscience research into resource and environmental challenges such as nuclear waste storage, geothermal energy and CO₂ capture. Students conduct literature reviews and produce class reports for presentation to a professional conference.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ENSGATE101</t>
+          <t>Earth's Resources</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
+          <t>ENSGATE201</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Environmental Studies</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3686,35 +3981,50 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ENVI</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ENSENVI312</t>
+          <t>ENSGATE101</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Earth's Resources</t>
+          <t>Provides key concepts in physics, chemistry, materials science, mathematics and modelling necessary for sustainability. Uses a case study to connect concepts to real‑world sustainability challenges and prepares students for 200‑level sustainability courses.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ENSGATE201</t>
+          <t>Sustainability Essentials I</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Environmental Studies</t>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3738,34 +4048,34 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>ENSGATE201</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Builds on Sustainability Essentials I. Applies tools and knowledge to a real‑world sustainability case study and allows students to delve deeper into aspects connected to their field of interest.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Sustainability Essentials II</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>ENSGATE101</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Sustainability Essentials I</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>Gateway</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>X</t>
@@ -3777,6 +4087,11 @@
         </is>
       </c>
       <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3790,32 +4105,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>SUST</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ENSGATE201</t>
+          <t>ENSSUST111</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sustainability Essentials II</t>
+          <t>Focuses on drivers and impacts of anthropogenic climate change on sea level, ocean acidification, ecology and society. Discusses adaptation and mitigation solutions, including renewable energy systems, carbon storage and climate‑adaptive planning, and examines climate governance and justice.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ENSGATE101</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Gateway</t>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sustainability</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3852,45 +4172,40 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ENSSUST111</t>
+          <t>ENSSUST112</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Teaches evaluation of environmental impacts of products, processes and services throughout their lifecycle. Emphasises strategic planning for a circular economy through hands‑on learning.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>Life Cycle Analysis &amp; Circular Economy</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>Sustainability</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3909,35 +4224,45 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ENSSUST112</t>
+          <t>ENSSUST113</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Life Cycle Analysis &amp; Circular Economy</t>
+          <t>Develops skills to recognise and handle misinformation. Discusses cognitive biases and detection methods, distinguishes real from fake experts, and includes case studies and a video project tackling a misinformation topic.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>Calling Bullshit</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Sustainability</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -3956,25 +4281,30 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ENSSUST113</t>
+          <t>ENSSUST211</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Calling Bullshit</t>
+          <t>Introduces renewable energy resources and technologies, discussing environmental, political and economic constraints. Covers energy storage and demand management and aims to balance energy supply and demand.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Energy &amp; Sustainability</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>ENSGATE101</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Sustainability</t>
         </is>
@@ -4008,40 +4338,45 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ENSSUST211</t>
+          <t>ENSSUST311</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Energy &amp; Sustainability</t>
+          <t>Teaches assessment of energy usage patterns and strategies for reducing consumption or transitioning to cleaner energy. Explores solar, wind and bioenergy solutions and includes technical and economic analysis; students deliver a report and presentation to a partner company.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ENSGATE101</t>
+          <t>Renewable System Design</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
+          <t>ENSGATE201</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Sustainability</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4060,40 +4395,35 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ENSSUST311</t>
+          <t>ENSSUST315</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Renewable System Design</t>
+          <t>Explores spatial engineering and geospatial technologies like GIS and remote sensing for addressing global challenges such as natural disasters, food shortages, resource decline and pollution. Emphasises hands‑on projects in disaster response, sustainable agriculture and environmental monitoring.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>Spatial Planning</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>ENSGATE201</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Environment &amp; Sustainability</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>Sustainability</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4102,40 +4432,60 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ENS</t>
+          <t>GOS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SUST</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ENSSUST315</t>
+          <t>GOSGATE102</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Spatial Planning</t>
+          <t>Examines law from legal, socio‑scientific and normative perspectives. Explores definitions, legal traditions and fields of law, investigates the relationship between law and society and the concept of justice, and includes case law, excursion to international legal organisations, interviews with practitioners and a moot court session.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ENSGATE201</t>
+          <t>Law, Society &amp; Justice</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Environment &amp; Sustainability</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sustainability</t>
+          <t>Government &amp; Society</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4149,50 +4499,55 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>HIST</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GOSGATE102</t>
+          <t>GOSHIST111</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Law, Society &amp; Justice</t>
+          <t>Provides a chronological overview of history from 1815 to the present. Discusses industrialisation, popular sovereignty and national self‑determination, and covers major economic, political and cultural developments including revolutions, world wars and the fall of communism.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>Modern History</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Gateway</t>
-        </is>
-      </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
+          <t>History</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4211,35 +4566,35 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GOSHIST111</t>
+          <t>GOSHIST112</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Modern History</t>
+          <t>Explores lives of ordinary people through the lens of gender from the 19th to 21st centuries. Uses storytelling across cultural forms; topics include slavery, mid‑20th‑century life, conversion therapy, queer cinema and banned books; engages with projects like Walking With Pride.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>Histories of Gender</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>History</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4250,6 +4605,11 @@
         </is>
       </c>
       <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4268,30 +4628,35 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GOSHIST112</t>
+          <t>GOSHIST211</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Histories of Gender</t>
+          <t>Examines the rise and fall of empires and the contested concept of empire. Discusses oppressive and benevolent features of empires, covers key theories on empires and power politics and analyses major historical examples.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>History of Empires</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>History</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4325,34 +4690,34 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GOSHIST211</t>
+          <t>GOSHIST213</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>History of Empires</t>
+          <t>Provides a chronological overview of warfare in the Western world from antiquity to the present. Covers weapons, technology, strategy, defence, mercenaries, cavalry, chivalry, Blitzkrieg, guerrilla warfare and nuclear arsenals, illustrating competition for mastery in Western history.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>Western Way of War</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>History</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>X</t>
@@ -4364,6 +4729,11 @@
         </is>
       </c>
       <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4382,45 +4752,50 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GOSHIST213</t>
+          <t>GOSHIST311</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Western Way of War</t>
+          <t>This course introduces students to Native American history and life from the 19th through the 21st century.  It argues that power, fear, misogyny, education, genocide, and resilience shape the Indigenous past and present. Topics we explore include the “Stolen Lives” of Indian children forcibly taken from their homes and placed in Indian Boarding Schools from the 1830’s through the 1990’s; Murdered and Missing Indigenous Women and Girls in the twenty-first century; and the individual and community forms of cultural resistance and environmental regeneration that connect past with present and future generations. We learn from the Native American scholars and 2Spirit youth that speak to and with the class. Exchange of cultural and intellectual knowledge also happens when we work with Lakota students to address contemporary challenges. Legislation, memoir, novels, and Indigenous children’s stories are central to our studies. So are the analyses of contemporary music and artistic expressions and exhibitions, as well as Hollywood and Indigenous film featuring Native American histories and lives.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>Native American Histories</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>History</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4439,45 +4814,50 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GOSHIST311</t>
+          <t>GOSHIST312</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Native American Histories</t>
+          <t>Guides students through the full arc of historical inquiry, from formulating research questions to engaging critically with sources. Emphasises methodological rigour and interdisciplinary thinking and culminates in a substantial research paper.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>History Research Seminar</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>History</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4491,32 +4871,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HIST</t>
+          <t>LAWJ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GOSHIST312</t>
+          <t>GOSLAWJ111</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>History Research Seminar</t>
+          <t>Offers a legal, historical and philosophical approach to human rights. Studies classical and modern philosophers, traces the rise of human rights, examines the US Bill of Rights and the French Declaration, and discusses human rights treaties.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>Human Rights: Law &amp; Philosophy</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>History</t>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Law</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4553,45 +4938,45 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GOSLAWJ111</t>
+          <t>GOSLAWJ211</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Human Rights: Law &amp; Philosophy</t>
+          <t>Examines moral and legal justifications for criminalisation and punishment. Investigates guiding principles of criminal law and justice, including criminal accountability, guilt, legality and fundamental principles, and applies theory through a simulated legal aid clinic.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Criminal Law &amp; Criminal Justice</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>GOSGATE102</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Law</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4610,40 +4995,50 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GOSLAWJ211</t>
+          <t>GOSLAWJ212</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Criminal Law &amp; Criminal Justice</t>
+          <t>Introduces rules, institutions and politics of public international law. Covers treaties, the UN, armed conflict, war crimes, refugee protection and climate change. Students analyse cases, debate issues and produce a podcast connecting law to global challenges.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>Introduction to Public International Law</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>GOSGATE102</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>Law</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4662,45 +5057,50 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GOSLAWJ212</t>
+          <t>GOSLAWJ213</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Introduction to Public International Law</t>
+          <t>Explores constitutional law and state organisation, using a comparative approach. Covers constitutionalism, separation of powers, judicial review, federalism and fundamental rights, and discusses constitution‑making, religious constitutions and constitutional backsliding.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>Comparative Constitutional Law</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>GOSGATE102</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Law</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4719,25 +5119,30 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GOSLAWJ213</t>
+          <t>GOSLAWJ311</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Comparative Constitutional Law</t>
+          <t>Examines principles of property law, tort law, contract law and other fields within private law. Uses comparisons of legal systems in four countries to explore rights and obligations arising from daily interactions.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>Principles of Private Law</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>GOSGATE102</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Law</t>
         </is>
@@ -4776,34 +5181,34 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GOSLAWJ311</t>
+          <t>GOSLAWJ312</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Principles of Private Law</t>
+          <t>Introduces the EU legal order. Studies institutions, framework, citizenship and the internal market using problem‑based exercises and guest lectures.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>Foundations of European Union Law</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>GOSGATE102</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>Law</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>X</t>
@@ -4815,6 +5220,11 @@
         </is>
       </c>
       <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4828,32 +5238,37 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LAWJ</t>
+          <t>PHIL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GOSLAWJ312</t>
+          <t>GOSPHIL111</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Foundations of European Union Law</t>
+          <t>Introduces central themes from Western philosophy over 2,500 years. Encourages inquiry into the significance of philosophical issues and their relation to other disciplines and teaches theoretical methods used by philosophers.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>GOSGATE102</t>
+          <t>Introduction to Western Philosophy</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Law</t>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Philosophy</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4890,34 +5305,34 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GOSPHIL111</t>
+          <t>GOSPHIL212</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Introduction to Western Philosophy</t>
+          <t>Explores theories of moral reasoning—virtue ethics, deontology, utilitarianism—and discusses moral knowledge, motivation, responsibility and the relation between happiness and pleasure. Applies theories to practical issues such as animal rights, privacy, future generations, war, punishment, disability and equality.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>Ethics</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>X</t>
@@ -4929,6 +5344,11 @@
         </is>
       </c>
       <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -4947,45 +5367,50 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GOSPHIL212</t>
+          <t>GOSPHIL214</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Ethics</t>
+          <t>Examines historical and modern work on the philosophy of mind. Discusses Descartes’ dualism, the nature of consciousness, AI and animal minds, personal identity, transformative experiences and the influence of technology on experience.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>Philosophy of Mind</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5004,25 +5429,30 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GOSPHIL214</t>
+          <t>GOSPHIL311</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Philosophy of Mind</t>
+          <t>Explores emotions from a philosophical perspective. Discusses nature and rationality of emotions, their role in ethics and art, and draws on historical and contemporary sources.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>Philosophy of Emotion</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>Philosophy</t>
         </is>
@@ -5032,17 +5462,17 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5061,32 +5491,32 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GOSPHIL311</t>
+          <t>GOSPHIL313</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Philosophy of Emotion</t>
+          <t>Investigates concepts of free will, the role of luck and openness of the future. Explores relations between free will, time and the self across multiple modules and contemporary debates.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>Free Will, Time &amp; the Self</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Philosophy</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5113,45 +5543,55 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PHIL</t>
+          <t>POLI</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GOSPHIL313</t>
+          <t>GOSPOLI111</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Free Will, Time &amp; the Self</t>
+          <t>Introduces political philosophy. Examines concepts such as authority, freedom, equality, democracy, human rights, pluralism, multiculturalism, poverty and environmental issues through classical and contemporary texts. Emphasises essay writing and presentations.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>Introduction to Political Philosophy</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Philosophy</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Political Science</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5170,45 +5610,50 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GOSPOLI111</t>
+          <t>GOSPOLI112</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Introduction to Political Philosophy</t>
+          <t>Provides analytical tools to compare political systems and democracies. Examines phenomena like democratic backsliding, decline of political parties, rise of populism, media changes, non‑majoritarian institutions and globalization’s impact on domestic politics.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>Foundations of Comparative Politics</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>Political Science</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5227,34 +5672,34 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GOSPOLI112</t>
+          <t>GOSPOLI212</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Foundations of Comparative Politics</t>
+          <t>Introduces basic theories of international relations and applies them to contemporary issues such as climate change, energy, humanitarian intervention, global crises and international relations between North-South and South-South actors. Includes a UN Security Council negotiation simulation.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>Theory of International Relations</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>Political Science</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J91" t="inlineStr">
         <is>
           <t>X</t>
@@ -5266,6 +5711,11 @@
         </is>
       </c>
       <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5284,25 +5734,30 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GOSPOLI212</t>
+          <t>GOSPOLI311</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Theory of International Relations</t>
+          <t>Introduces EU politics. Outlines actors, institutions and decision‑making rules; examines responses to crises; and employs various approaches to study EU politics and policy‑making.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>European Union Politics</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>Political Science</t>
         </is>
@@ -5341,45 +5796,40 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GOSPOLI311</t>
+          <t>GOSPOLI312</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>European Union Politics</t>
+          <t>Investigates public policy in the context of globalization. Uses a case study on sugar to examine policy‑making phases and alternative conceptualisations across national and international arenas. Students write policy memos.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>Public Policy Analysis</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>Political Science</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5398,35 +5848,50 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GOSPOLI312</t>
+          <t>GOSPOLI313</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Public Policy Analysis</t>
+          <t>Introduces Peace &amp; Conflict Studies. Examines definitions of peace and conflict; analyzes conflict causation, violence typologies and radicalisation; applies reconciliation and conflict‑transformation models to real‑world scenarios through lectures and portfolio work.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>Peace &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>Political Science</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5440,32 +5905,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>POLI</t>
+          <t>SOCI</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GOSPOLI313</t>
+          <t>GOSSOCI111</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Peace &amp; Conflict</t>
+          <t>Introduces concepts, theories and methods of sociology. Examines socio‑historical context of key authors like Marx, Weber, Durkheim and Du Bois, and encourages exploration of social problems related to race, gender and class through theoretical approaches and methodologies.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>Introduction to Sociology</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Political Science</t>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5502,34 +5972,34 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GOSSOCI111</t>
+          <t>GOSSOCI212</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Introduction to Sociology</t>
+          <t>Introduces qualitative research methodology. Covers designing questions, interpreting meaning and conducting small team projects, while reflecting on complexity and power dynamics in social research.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>Qualitative Research Methodology</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>Sociology</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J96" t="inlineStr">
         <is>
           <t>X</t>
@@ -5541,6 +6011,11 @@
         </is>
       </c>
       <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5559,32 +6034,32 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GOSSOCI212</t>
+          <t>GOSSOCI214</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Qualitative Research Methodology</t>
+          <t>Examines the trajectory of sociology within the culture of imperialism and colonial responses. Studies leading social theories and debates about modernity and critically engages with sociological discourses.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>Modern Sociology</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>Sociology</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5616,40 +6091,45 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GOSSOCI214</t>
+          <t>GOSSOCI215</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Modern Sociology</t>
+          <t>Focuses on social movement theories and environmental justice. Uses case studies from the Environmental Justice Atlas and integrates perspectives such as feminism, anti‑colonialism, degrowth and environmental peacebuilding to encourage civic engagement.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>Social Movements &amp; Environmental Justice</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>Sociology</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5668,27 +6148,37 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GOSSOCI215</t>
+          <t>GOSSOCI311</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Social Movements &amp; Environmental Justice</t>
+          <t>Examines contemporary sociological debates about civil society through critical tradition, neo‑functionalism and decolonial critiques. Includes research group projects with NGOs or civil society organizations that translate conceptual insights into empirical analysis.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>New Issues in Contemporary Social Theory</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Government &amp; Society</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>Sociology</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5710,55 +6200,56 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GOS</t>
+          <t>HCB</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SOCI</t>
+          <t>BIOM</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GOSSOCI311</t>
+          <t>HCBBIOM111</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>New Issues in Contemporary Social Theory</t>
+          <t>Public health is about changing the world. From pandemics to lifestyle-related diseases, from screening for disease to improving water and air quality, it asks: how can we improve to keep the population healthy?_x000D_
+But how do we know what actually works? In this course you will dive into epidemiology: the science behind public health. You will learn how to study disease, risks, and changes over time, and how to critically evaluate evidence. Because behind every public health decision lies a question of evidence, and by the end of this course, you will be equipped to engage with it. This course invites you to look beyond the lab, the hospital, and the library, into the wider world where health is shaped. What matters most if we truly care about health, and how can we influence that?</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>Epidemiology &amp; Public Health</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Government &amp; Society</t>
-        </is>
-      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sociology</t>
+          <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
+          <t>Biomedical Science</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5777,25 +6268,30 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HCBBIOM111</t>
+          <t>HCBBIOM211</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Epidemiology &amp; Public Health</t>
+          <t>Introduces human body functioning using imaging, surface anatomy and dissection materials. Shows how anatomy serves function and discusses ethical considerations of learning from the dead.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Functional Anatomy</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
+          <t>HCBGATE101</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>Biomedical Science</t>
         </is>
@@ -5811,6 +6307,11 @@
         </is>
       </c>
       <c r="N101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5829,25 +6330,30 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HCBBIOM211</t>
+          <t>HCBBIOM311</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Functional Anatomy</t>
+          <t>Covers the science of drugs—their origin, composition, kinetics, therapeutic use and toxicity. Discusses drug targets, interactions and kinetics, enabling students to explain therapies in terms of molecular targets and physiological consequences.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t>Pharmacology</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t>HCBGATE101</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>Biomedical Science</t>
         </is>
@@ -5886,34 +6392,34 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HCBBIOM311</t>
+          <t>HCBBIOM312</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Pharmacology</t>
+          <t>Explores fundamental processes in immunology such as recognition of self vs non‑self, lymphocyte receptor development and innate and adaptive immune responses. Examines host‑pathogen interactions, inflammation, tissue damage and immunopathology.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>Infection &amp; Immunity</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>HCBGATE101</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>Biomedical Science</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J103" t="inlineStr">
         <is>
           <t>X</t>
@@ -5925,6 +6431,11 @@
         </is>
       </c>
       <c r="N103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5943,45 +6454,50 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HCBBIOM312</t>
+          <t>HCBBIOM313</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Infection &amp; Immunity</t>
+          <t>Examines molecular and cellular defects triggering pathologies. Presents clinical cases, discusses disease mechanisms and treatments across systems and includes an assignment to invent an imaginary disease.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>Mechanisms of Disease</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t>HCBGATE101</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>Biomedical Science</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -5995,50 +6511,55 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BIOM</t>
+          <t>COGN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HCBBIOM313</t>
+          <t>HCBCOGN112</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Mechanisms of Disease</t>
+          <t>Examines evolution and complexity of brains. Explores animal cognition, welfare and research ethics and studies how brain regions and rhythms regulate behaviour through interactive assignments.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>HCBGATE101</t>
+          <t>Neurobiology</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Biomedical Science</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Cognitive Science</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6057,45 +6578,45 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HCBCOGN112</t>
+          <t>HCBCOGN212</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Neurobiology</t>
+          <t>Explores neural mechanisms behind perception and action. Examines how the brain processes sensory information and guides goal‑directed behaviour using methods from cognitive neuroscience and neuropsychology.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Perception &amp; Action</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
+          <t>HCBGATE102</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>Cognitive Science</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6114,27 +6635,37 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>HCBCOGN212</t>
+          <t>HCBCOGN311</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Perception &amp; Action</t>
+          <t>Deepens understanding of neurophysiology and neuroanatomy. Explores higher‑level cognitive functions—memory, emotion, social cognition, executive functioning and language—and engages with current research while designing experiments.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
+          <t>Higher Order Functions</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t>HCBGATE102</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>Cognitive Science</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6161,50 +6692,55 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>COGN</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>HCBCOGN311</t>
+          <t>HCBGATE101</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Higher Order Functions</t>
+          <t>Introduces biochemistry, macromolecules, cells, organ systems, DNA and cell function. Connects fundamentals to health and disease and serves as a starting point for medicine, biomedical science, life science or public health; no lab experience needed.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>Foundation of Life, Health &amp; Biomedicine</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Cognitive Science</t>
-        </is>
-      </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6218,35 +6754,75 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>COGN</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>HCBCOGN312</t>
+          <t>HCBGATE102</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Psycholinguistics</t>
+          <t>Explores why people behave as they do and how brain injuries affect mental processes. Discusses nature and nurture, introduces brain anatomy and psychological theories, and provides a gateway to cognitive science and clinical psychology.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>Introduction to Brain &amp; Behavior</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Cognitive Science</t>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6260,40 +6836,40 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
+          <t>HCBLIFE211</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Provides foundation for practical applications in life science. Focuses on cellular biology of eukaryotes and prokaryotes, revisits concepts from introductory courses, examines current research and encourages evaluating reproducibility and modernising methods.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Molecular Cell Biology</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t>HCBGATE101</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Foundation of Life, Health &amp; Biomedicine</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Gateway</t>
-        </is>
-      </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
+          <t>Life Science</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6304,6 +6880,11 @@
         </is>
       </c>
       <c r="N110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6317,37 +6898,37 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>HCBLIFE212</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Introduction to Brain &amp; Behavior</t>
+          <t>Studies normal functioning of the human body, covering structure‑function relationships, energy handling, homeostasis, signalling, organ systems and integration of their functions.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Human Physiology</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
+          <t>HCBGATE101</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Gateway</t>
-        </is>
-      </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Life Science</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6355,27 +6936,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="K111" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="M111" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6399,30 +6965,35 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HCBLIFE211</t>
+          <t>HCBLIFE213</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Molecular Cell Biology</t>
+          <t>Explores the chemistry of life and biomolecules such as proteins, sugars, lipids and nucleic acids. Discusses metabolic pathways, the role of biomolecules in health and disease and applications in medicine, biotechnology and sustainability.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
+          <t>Biochemistry</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t>HCBGATE101</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>Life Science</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6456,34 +7027,34 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>HCBLIFE212</t>
+          <t>HCBLIFE214</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Human Physiology</t>
+          <t>Introduces biochemical and molecular laboratory work. Covers themes like blood, proteins, bacteria, DNA and bioinformatics and provides a foundation for clinical and biomedical research.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
+          <t>Life Science Laboratory</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t>HCBGATE101</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>Life Science</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J113" t="inlineStr">
         <is>
           <t>X</t>
@@ -6495,6 +7066,11 @@
         </is>
       </c>
       <c r="N113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6513,45 +7089,50 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HCBLIFE213</t>
+          <t>HCBLIFE311</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Biochemistry</t>
+          <t>Covers general and molecular pathology and genetics. Studies cell injury, death, inflammation, immunity, tissue repair, regeneration, fibrosis and neoplasia, examines genetic mutations and diseases, and discusses genetic testing and ethical considerations.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
+          <t>Molecular Pathology &amp; Genetics</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t>HCBGATE101</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>Life Science</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6565,50 +7146,55 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>PSYC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HCBLIFE214</t>
+          <t>HCBPSYC111</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Life Science Laboratory</t>
+          <t>Covers main theories, findings and principles of social psychology, emphasising its scientific approach to understanding how people’s feelings, thoughts and behaviour are influenced by the presence of others.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>HCBGATE101</t>
+          <t>Social Psychology</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Life Science</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr">
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Psychology</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6622,32 +7208,37 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>PSYC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HCBLIFE311</t>
+          <t>HCBPSYC211</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Molecular Pathology &amp; Genetics</t>
+          <t>The course is necessary for students who want to pursue master programs in psychology and adjacent disciplines, as well as research masters in the medical domain. It is highly recommended also for all those who want to be researchers in other domains. In addition to technical training, the course emphasizes clear academic communication. It will equip you with the skills necessary to apply advanced statistical techniques to real-world research problems. With a focus on practical application through case studies and data analysis projects, You will be able to choose the appropriate statistical model for various research scenarios and address common challenges in data interpretation.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>HCBGATE101</t>
+          <t>Statistics &amp; Experimental Methods</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Life Science</t>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6655,17 +7246,17 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6684,45 +7275,50 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HCBPSYC111</t>
+          <t>HCBPSYC212</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Social Psychology</t>
+          <t>Provides a deep dive into factors shaping mental health. Teaches critical thinking, explores the bio‑psycho‑social approach and covers mental disorders, research findings and assessment techniques.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Abnormal Psychology</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
+          <t>HCBGATE102</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>Psychology</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr">
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6741,45 +7337,50 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>HCBPSYC211</t>
+          <t>HCBPSYC311</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Statistics &amp; Experimental Methods</t>
+          <t>Uses a biopsychosocial approach to explore how biological, psychological and socio‑cultural factors influence health and illness. Covers theories, research and interventions and focuses on the role of psychological expertise in medical settings.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Medical &amp; Health Psychology</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
+          <t>HCBGATE102</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>Psychology</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6798,45 +7399,50 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HCBPSYC212</t>
+          <t>HCBPSYC312</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Abnormal Psychology</t>
+          <t>Introduces key theories, methods and practices in psychodiagnostics and psychotherapy. Covers psychological assessment techniques and psychotherapeutic approaches and builds practical competencies and clinical skills.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
+          <t>Psychodiagnostics &amp; Psychotherapies</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t>HCBGATE102</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t>Psychology</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr">
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6855,34 +7461,34 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HCBPSYC311</t>
+          <t>HCBPSYC313</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Medical &amp; Health Psychology</t>
+          <t>This course guides you through combining results from multiple studies using systematic reviews and meta-analysis a method now essential in psychology, medicine, social science and other disciplines. Want to know what really works? Gain hands-on skills in research synthesis that inform evidence-based policy and practice. You’ll search literature, manage data, and present findings that matter. Learn to calculate effect sizes, synthesize results and assess bias using R.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
+          <t>Advanced Research Seminar</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t>HCBGATE102</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t>Psychology</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J120" t="inlineStr">
         <is>
           <t>X</t>
@@ -6894,6 +7500,11 @@
         </is>
       </c>
       <c r="N120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6912,45 +7523,50 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HCBPSYC312</t>
+          <t>HCBPSYC314</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Psychodiagnostics &amp; Psychotherapies</t>
+          <t>Explores human development across the lifespan. Examines physical, cognitive, emotional and social changes from prenatal life to old age and develops critical thinking about factors influencing individual uniqueness.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
+          <t>Lifespan Developmental Psychology</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t>HCBGATE102</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>Health, Cognition &amp; Behavior</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>Psychology</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr">
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6959,37 +7575,42 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>HCB</t>
+          <t>MCC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PSYC</t>
+          <t>COMM</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HCBPSYC313</t>
+          <t>MCCCOMM111</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Advanced Research Seminar</t>
+          <t>Teaches how to craft persuasive messages, influence opinions, inspire action and connect people. Draws on historical communicators from Aristotle to Barack Obama and applies stylistic techniques to students’ own writing and speaking.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>The Art of Rhetorical Communication</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Media, Culture &amp; Communication</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Communication</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7016,37 +7637,42 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>HCB</t>
+          <t>MCC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PSYC</t>
+          <t>COMM</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HCBPSYC314</t>
+          <t>MCCCOMM112</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Lifespan Developmental Psychology</t>
+          <t>This course aims to develop basic skills and strategies necessary to successfully handle uncomplicated oral and written communication in Dutch in a variety of social situations that you may encounter in daily life in the Netherlands. The emphasis in the course will be on speaking in Dutch in day-to-day situations on the one hand and understanding Dutch culture on the other hand. At the end of the course students can orally express and write about themselves in Dutch, who they are, describe their family background, and interact with others in a simple way.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>HCBGATE102</t>
+          <t>Dutch</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Health, Cognition &amp; Behavior</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Media, Culture &amp; Communication</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Communication</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7054,17 +7680,22 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O123" t="inlineStr">
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7073,37 +7704,42 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>HCB</t>
+          <t>MCC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PSYC</t>
+          <t>COMM</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HCBPSYC315</t>
+          <t>MCCCOMM211</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Youth Resilience to Extremism</t>
+          <t>Explores how linguistic choices inform meaning and interpretation in literary and non-fiction contexts. Introduces theoretical frameworks for close reading and addresses power dynamics, obligation, uncertainty and ideological undertones in language.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
+          <t>Style &amp; Meaning</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Health, Cognition &amp; Behavior</t>
-        </is>
-      </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Media, Culture &amp; Communication</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Communication</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7117,6 +7753,11 @@
         </is>
       </c>
       <c r="N124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7135,45 +7776,45 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MCCCOMM111</t>
+          <t>MCCCOMM212</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>The Art of Rhetorical Communication</t>
+          <t>Examines how the climate crisis is communicated and contested. Analyzes texts, films, exhibitions, protest art, slogans and social media alongside theory and case studies, teaching students to dissect arguments and culminating in a project where students enter the debate.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
+          <t>Communicating the Climate Crisis</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7192,50 +7833,45 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MCCCOMM112</t>
+          <t>MCCCOMM213</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Dutch</t>
+          <t>Develops persuasive speaking skills by applying rhetorical theory in the real world. Students work with local primary school children, building public-speaking skills and empowering them to find their voices.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
+          <t>Rhetoric in Action</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr">
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7254,25 +7890,30 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MCCCOMM211</t>
+          <t>MCCCOMM311</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Style &amp; Meaning</t>
+          <t>Explores ethical persuasion and climate communication. Students learn persuasive communication models and frameworks and collaborate with climate scientists at the Delta Climate Centre to produce sustainability messaging on water, food and energy.</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
+          <t>Persuasive Communication</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
@@ -7311,40 +7952,50 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MCCCOMM212</t>
+          <t>MCCCOMM312</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Communicating the Climate Crisis</t>
+          <t>Explores meaning-making through creative expression. Students study and practice poetic forms, experiment with sonic poetry, performance and other unconventional forms of communication, engage with theoretical texts and produce their own creative work.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
+          <t>Creative Communication Laboratory</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr">
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7358,32 +8009,37 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>COMM</t>
+          <t>HEAM</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MCCCOMM213</t>
+          <t>MCCHEAM111</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Rhetoric in Action</t>
+          <t>Provides an introduction to Western art history, tracing major artistic movements from the late Middle Ages to the present. Through close study of key paintings and their makers, students gain insight into evolving styles, techniques and cultural influences.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
+          <t>Introduction to Western Art History</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Communication</t>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Cultural Heritage</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7392,6 +8048,11 @@
         </is>
       </c>
       <c r="K129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7410,37 +8071,37 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>COMM</t>
+          <t>HEAM</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MCCCOMM311</t>
+          <t>MCCHEAM112</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Persuasive Communication</t>
+          <t>Explores ancient craft production from around the world. Examines how making objects shaped human development and how ancient solutions can inform modern sustainability.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
+          <t>Introduction to World Archaeology</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Cultural Heritage</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7454,6 +8115,11 @@
         </is>
       </c>
       <c r="N130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7467,50 +8133,45 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>COMM</t>
+          <t>HEAM</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MCCCOMM312</t>
+          <t>MCCHEAM211</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Creative Communication Laboratory</t>
+          <t>Examines the artistic, historical and ethical dimensions of African art. Highlights distinct forms and cultural significance, considers influence on Western modernism and addresses looting, colonial-era acquisitions and repatriation efforts.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
+          <t>African Art &amp; Heritage</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O131" t="inlineStr">
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Cultural Heritage</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7529,45 +8190,45 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MCCHEAM111</t>
+          <t>MCCHEAM212</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Introduction to Western Art History</t>
+          <t>This course examines the painting, sculpture, and architecture of Renaissance Italy and the extensive artistic connections that linked the Italian peninsula to other regions of the world. By exploring a range of geographical contexts, from the Islamic courts of the Eastern Mediterranean and the commercial routes connecting Europe, Asia, and Africa to the newly encountered territories of the Americas, students will examine how trade, colonization, and cross-cultural exchange shaped the production and meaning of Renaissance art.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
+          <t>Renaissance Italy &amp; Global Mediterranean</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>Cultural Heritage</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7586,45 +8247,45 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MCCHEAM112</t>
+          <t>MCCHEAM213</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Introduction to World Archaeology</t>
+          <t>Explores the archaeology of community and democracy in early-democratic Greece, seeking ancient lessons on community decision-making.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
+          <t>Greek Archaeology</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>Cultural Heritage</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O133" t="inlineStr">
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7643,25 +8304,30 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MCCHEAM211</t>
+          <t>MCCHEAM312</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>African Art &amp; Heritage</t>
+          <t>Examines debates on modern art through various themes. Focuses on the relationship between art and its presentation in museums and exhibitions, exploring curatorial practices and exhibition strategies.</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
+          <t>Modern Art &amp; Modern Museums</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>Cultural Heritage</t>
         </is>
@@ -7671,7 +8337,17 @@
           <t>X</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7690,25 +8366,32 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MCCHEAM212</t>
+          <t>MCCHEAM315</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Renaissance Italy &amp; Global Mediterranean</t>
+          <t>In the modern world democracy is associated with participation, rationality and freedom. In this course, we go back to the roots of democracy in ancient Greece, when to a modern observer, it was not very democratic at all: foreigners, slaves and women were excluded from elections and political decision-making. Even so, the inclusion of all classes, also the poor, in politics was after antiquity not achieved until the mid-nineteenth century._x000D_
+Ancient commentators criticised Athenian democracy for being too extreme just because of this broad inclusion. They argued that many were too uneducated, too emotional, and too irrational to see through the cheap play on emotions by demagogues and would-be tyrants._x000D_
+This course investigates how Athenian democracy was built, how it was intertwined with myth and religion, and expressed in art, literature and architecture. It traces the loci of democracy in archaeology, and analyses its temporary collapse in the crisis of the late fifth century BC. Most importantly, we put ourselves in our socio-political ancestors’ shoes by engaging in a simulation of the Athenian assembly, in which we have to make decisions that will change our lives forever. In doing so, we use the ancient heritage of democracy for an experiment in applied sociology – to not only understand, but to feel the meaning of political decision-making.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
+          <t>Heritage &amp; Ancient Democracy</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>Cultural Heritage</t>
         </is>
@@ -7742,40 +8425,40 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MCCHEAM213</t>
+          <t>MCCHEAM316</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Greek Archaeology</t>
+          <t>This course examines the history of art history as an academic discipline, tracing how scholars have understood and interpreted art from the sixteenth century to the present. Through critical readings of influential texts by figures such as Aby Warburg, Erwin Panofsky, Ernst Gombrich, Michel Foucault, and Jacques Derrida, students explore the major ideas and methodologies that have shaped the field. Topics include art and history, aesthetics, meaning and interpretation, authorship and identity, and the challenges of art history in a globalized world.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
+          <t>Writing Art's Histories</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="H136" t="inlineStr">
         <is>
           <t>Cultural Heritage</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr">
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7789,50 +8472,55 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HEAM</t>
+          <t>LITR</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MCCHEAM312</t>
+          <t>MCCLITR111</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Modern Art &amp; Modern Museums</t>
+          <t>Introduces what literature is, why we read it and how to interpret it. Covers fiction, poetry, drama, non‑fiction and film narration, exploring various literary forms and genres such as graphic narratives and romance novels.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
+          <t>Introduction to Literary Studies</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Cultural Heritage</t>
-        </is>
-      </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
+          <t>Literature</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7846,32 +8534,37 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>HEAM</t>
+          <t>LITR</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MCCHEAM315</t>
+          <t>MCCLITR112</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Heritage &amp; Ancient Democracy</t>
+          <t>Provides a chronological overview of literature from the epic of Gilgamesh to post‑modernity. Reads literary and critical texts that explore human experience and teaches how to approach literature’s ambiguities and trace themes across ages.</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
+          <t>Great Literary Works</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Cultural Heritage</t>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Literature</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7885,6 +8578,11 @@
         </is>
       </c>
       <c r="N138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7898,35 +8596,50 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HEAM</t>
+          <t>LITR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MCCHEAM316</t>
+          <t>MCCLITR211</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Writing Art's Histories</t>
+          <t>Investigates myths from around the world—from Gilgamesh to the Ramayana, Greek and Norse myths. Explores how myths underpin literature and connects them to contemporary global cultures.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
+          <t>World Myth &amp; Literature</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Cultural Heritage</t>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Literature</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -7950,34 +8663,34 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MCCLITR111</t>
+          <t>MCCLITR212</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Introduction to Literary Studies</t>
+          <t>Examines autobiographical and travel writing. Explores how individuals write about self, identity and bodily experience; discusses tropes and models used to represent human experience; and considers memory and imagination in writing.</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
+          <t>Life &amp; Travel Writing</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J140" t="inlineStr">
         <is>
           <t>X</t>
@@ -7989,6 +8702,11 @@
         </is>
       </c>
       <c r="N140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8007,25 +8725,30 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MCCLITR112</t>
+          <t>MCCLITR311</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Great Literary Works</t>
+          <t>Studies complex links between literary and film narratives. Analyzes formal aspects of both media, discusses adaptation, intertextuality, viewer participation and narrative dynamics, and allows students to research topics like literature‑to‑film adaptation and cross‑cultural themes.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
+          <t>Film &amp; Text</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="H141" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
@@ -8064,45 +8787,45 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MCCLITR211</t>
+          <t>MCCLITR312</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>World Myth &amp; Literature</t>
+          <t>Examines how different perspectives—humanist, feminist, Marxist, cultural minority and psychoanalytic—affect reading and interpretation. Students undertake a research project applying selected perspectives to texts.</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
+          <t>Perspectives on Literary Meaning</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="H142" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8116,32 +8839,37 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>LITR</t>
+          <t>MEDI</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MCCLITR212</t>
+          <t>MCCMEDI111</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Life &amp; Travel Writing</t>
+          <t>Introduces film and media as systems of meaning and cultural production. Examines how images, narratives and technologies shape perception, identity and power; covers film storytelling, representation and genres; and develops critical engagement skills.</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
+          <t>Introduction to Film &amp; Media</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Literature</t>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8173,50 +8901,55 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>LITR</t>
+          <t>MEDI</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MCCLITR311</t>
+          <t>MCCMEDI112</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Film &amp; Text</t>
+          <t>Explores media technologies before digital culture. Studies cassette tapes, typewriters and early printing as material objects that carry meaning; includes hands‑on experiments; no technical background required.</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
+          <t>Media Archaeology</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Literature</t>
-        </is>
-      </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr">
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8230,45 +8963,50 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>LITR</t>
+          <t>MEDI</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MCCLITR312</t>
+          <t>MCCMEDI211</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Perspectives on Literary Meaning</t>
+          <t>Explores how media shape attitudes and provide answers through examples from TV and TikTok. Examines messages that teach fear, pity, admiration and allyship.</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
+          <t>From T.V. to TikTok</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Literature</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O145" t="inlineStr">
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8287,34 +9025,34 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MCCMEDI111</t>
+          <t>MCCMEDI212</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Introduction to Film &amp; Media</t>
+          <t>Examines representation of environmental concerns through visual culture. Explores the Anthropocene, animal representation, deep time, biocentrism, contested nature, indigenous and postcolonial media; analyzes how media shape environmental understanding; and includes a paper or media project.</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
+          <t>Media &amp; the Environment</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="H146" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J146" t="inlineStr">
         <is>
           <t>X</t>
@@ -8326,6 +9064,11 @@
         </is>
       </c>
       <c r="N146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8344,45 +9087,50 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MCCMEDI112</t>
+          <t>MCCMEDI311</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Media Archaeology</t>
+          <t>Investigates storytelling and power in relation to race. Examines Afrofuturism and systemic racism and guides students in creating podcasts that explore links between past and present.</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
+          <t>Media &amp; Race</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="H147" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -8401,211 +9149,50 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MCCMEDI211</t>
+          <t>MCCMEDI312</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>From T.V. to TikTok</t>
+          <t>Introduces development of the documentary form. Students write a theoretical paper and produce a short documentary film, fostering understanding of documentary diversity and providing analytical tools for documentary study.</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
+          <t>The Documentary</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>Media, Culture &amp; Communication</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>MCC</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>MEDI</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>MCCMEDI212</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Media &amp; the Environment</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>MCC</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>MEDI</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>MCCMEDI311</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Media &amp; Race</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>MCC</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>MEDI</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>MCCMEDI312</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>The Documentary</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Media, Culture &amp; Communication</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr">
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
         <is>
           <t>X</t>
         </is>
